--- a/grupos/6APV - Estadisticos 20212.xlsx
+++ b/grupos/6APV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -179,12 +179,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
@@ -218,12 +218,156 @@
     <t>BELLO</t>
   </si>
   <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>XOLIO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>NAVA</t>
+  </si>
+  <si>
+    <t>ARENAS</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>CARLO HUMBERTO</t>
+  </si>
+  <si>
+    <t>JESUS ALBERTO</t>
+  </si>
+  <si>
+    <t>JOSMAR ANTONIO</t>
+  </si>
+  <si>
+    <t>GIOVANNI</t>
+  </si>
+  <si>
+    <t>ARELY</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>VICTOR YAHIR</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>ANDREA YAMILET</t>
+  </si>
+  <si>
+    <t>JESUS ARMANDO</t>
+  </si>
+  <si>
+    <t>GWINETH</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>HERSON ELIAS</t>
+  </si>
+  <si>
+    <t>JOEL</t>
+  </si>
+  <si>
     <t>CARDENAS</t>
   </si>
   <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
     <t>CORTES</t>
   </si>
   <si>
@@ -236,72 +380,18 @@
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>MANUEL</t>
   </si>
   <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
     <t>PATIÑO</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>XOLIO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>NAVA</t>
-  </si>
-  <si>
-    <t>ARENAS</t>
-  </si>
-  <si>
     <t>AMADOR</t>
   </si>
   <si>
@@ -317,69 +407,21 @@
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>CARLO HUMBERTO</t>
-  </si>
-  <si>
-    <t>JESUS ALBERTO</t>
-  </si>
-  <si>
-    <t>JOSMAR ANTONIO</t>
-  </si>
-  <si>
     <t>KEVIN HONAM</t>
   </si>
   <si>
-    <t>GIOVANNI</t>
-  </si>
-  <si>
     <t>SAUL ESTEBAN</t>
   </si>
   <si>
@@ -392,15 +434,6 @@
     <t>ABRAHAM</t>
   </si>
   <si>
-    <t>ARELY</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
     <t>JESUS MANUEL</t>
   </si>
   <si>
@@ -410,52 +443,19 @@
     <t>LUZ ABRIL</t>
   </si>
   <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>VICTOR YAHIR</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>ANDREA YAMILET</t>
-  </si>
-  <si>
     <t>CRISTOPHER ENRIQUE</t>
   </si>
   <si>
     <t>CARLOS FERNANDO</t>
   </si>
   <si>
-    <t>JESUS ARMANDO</t>
-  </si>
-  <si>
     <t>CIELO IVETTE</t>
   </si>
   <si>
-    <t>GWINETH</t>
-  </si>
-  <si>
     <t>YOSEF OMAR</t>
   </si>
   <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
     <t>EDGAR</t>
-  </si>
-  <si>
-    <t>ADAN</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>HERSON ELIAS</t>
-  </si>
-  <si>
-    <t>JOEL</t>
   </si>
 </sst>
 </file>
@@ -947,7 +947,7 @@
         <v>10</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>8</v>
@@ -1001,7 +1001,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -1024,7 +1024,7 @@
         <v>8</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -1078,7 +1078,7 @@
         <v>8</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
         <v>5</v>
@@ -1101,7 +1101,7 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>10</v>
@@ -1155,7 +1155,7 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -1178,7 +1178,7 @@
         <v>-1</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>5</v>
@@ -1232,7 +1232,7 @@
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>5</v>
@@ -1255,7 +1255,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E8">
         <v>6</v>
@@ -1264,7 +1264,7 @@
         <v>5</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H8">
         <v>-1</v>
@@ -1309,7 +1309,7 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>6</v>
@@ -1318,7 +1318,7 @@
         <v>5</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1332,7 +1332,7 @@
         <v>10</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E9">
         <v>9</v>
@@ -1386,7 +1386,7 @@
         <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1409,7 +1409,7 @@
         <v>10</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E10">
         <v>10</v>
@@ -1418,7 +1418,7 @@
         <v>10</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H10">
         <v>-1</v>
@@ -1463,7 +1463,7 @@
         <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>10</v>
@@ -1472,7 +1472,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1486,7 +1486,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E11">
         <v>9</v>
@@ -1495,7 +1495,7 @@
         <v>9</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H11">
         <v>-1</v>
@@ -1540,7 +1540,7 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1549,7 +1549,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1563,7 +1563,7 @@
         <v>-1</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -1617,7 +1617,7 @@
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1640,7 +1640,7 @@
         <v>10</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <v>7</v>
@@ -1649,7 +1649,7 @@
         <v>6</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H13">
         <v>-1</v>
@@ -1694,7 +1694,7 @@
         <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1703,7 +1703,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1717,7 +1717,7 @@
         <v>10</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E14">
         <v>8</v>
@@ -1726,7 +1726,7 @@
         <v>7</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -1771,7 +1771,7 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1780,7 +1780,7 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1794,7 +1794,7 @@
         <v>10</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E15">
         <v>10</v>
@@ -1848,7 +1848,7 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>10</v>
@@ -1880,7 +1880,7 @@
         <v>7</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -1934,7 +1934,7 @@
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1948,7 +1948,7 @@
         <v>10</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E17">
         <v>9</v>
@@ -1957,7 +1957,7 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H17">
         <v>-1</v>
@@ -2002,7 +2002,7 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -2011,7 +2011,7 @@
         <v>10</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2025,7 +2025,7 @@
         <v>8</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E18">
         <v>7</v>
@@ -2034,7 +2034,7 @@
         <v>8</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H18">
         <v>-1</v>
@@ -2079,7 +2079,7 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -2088,7 +2088,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2102,7 +2102,7 @@
         <v>10</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E19">
         <v>9</v>
@@ -2111,7 +2111,7 @@
         <v>10</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H19">
         <v>-1</v>
@@ -2156,7 +2156,7 @@
         <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>9</v>
@@ -2165,7 +2165,7 @@
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2179,7 +2179,7 @@
         <v>-1</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E20">
         <v>6</v>
@@ -2188,7 +2188,7 @@
         <v>6</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -2233,7 +2233,7 @@
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>6</v>
@@ -2242,7 +2242,7 @@
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2256,7 +2256,7 @@
         <v>10</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E21">
         <v>8</v>
@@ -2310,7 +2310,7 @@
         <v>10</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2333,7 +2333,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>5</v>
@@ -2387,7 +2387,7 @@
         <v>7</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>5</v>
@@ -2410,7 +2410,7 @@
         <v>10</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E23">
         <v>10</v>
@@ -2419,7 +2419,7 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H23">
         <v>-1</v>
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>10</v>
@@ -2473,7 +2473,7 @@
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2487,7 +2487,7 @@
         <v>-1</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E24">
         <v>5</v>
@@ -2541,7 +2541,7 @@
         <v>-1</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W24">
         <v>5</v>
@@ -2564,7 +2564,7 @@
         <v>10</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E25">
         <v>8</v>
@@ -2573,7 +2573,7 @@
         <v>7</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H25">
         <v>-1</v>
@@ -2618,7 +2618,7 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>8</v>
@@ -2627,7 +2627,7 @@
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2641,7 +2641,7 @@
         <v>10</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E26">
         <v>8</v>
@@ -2650,7 +2650,7 @@
         <v>8</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H26">
         <v>-1</v>
@@ -2695,7 +2695,7 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>8</v>
@@ -2704,7 +2704,7 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2718,7 +2718,7 @@
         <v>10</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E27">
         <v>9</v>
@@ -2772,7 +2772,7 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>9</v>
@@ -2795,7 +2795,7 @@
         <v>10</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E28">
         <v>10</v>
@@ -2804,7 +2804,7 @@
         <v>10</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H28">
         <v>-1</v>
@@ -2849,7 +2849,7 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>10</v>
@@ -2858,7 +2858,7 @@
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2949,7 +2949,7 @@
         <v>-1</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E30">
         <v>5</v>
@@ -3003,7 +3003,7 @@
         <v>-1</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W30">
         <v>5</v>
@@ -3026,7 +3026,7 @@
         <v>10</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E31">
         <v>9</v>
@@ -3035,7 +3035,7 @@
         <v>9</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H31">
         <v>-1</v>
@@ -3080,7 +3080,7 @@
         <v>10</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>9</v>
@@ -3089,7 +3089,7 @@
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3103,7 +3103,7 @@
         <v>-1</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E32">
         <v>7</v>
@@ -3112,7 +3112,7 @@
         <v>7</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H32">
         <v>-1</v>
@@ -3157,7 +3157,7 @@
         <v>-1</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W32">
         <v>7</v>
@@ -3166,7 +3166,7 @@
         <v>7</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3180,7 +3180,7 @@
         <v>9</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E33">
         <v>5</v>
@@ -3234,7 +3234,7 @@
         <v>9</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W33">
         <v>5</v>
@@ -3257,7 +3257,7 @@
         <v>-1</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E34">
         <v>5</v>
@@ -3266,7 +3266,7 @@
         <v>6</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H34">
         <v>-1</v>
@@ -3311,7 +3311,7 @@
         <v>-1</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W34">
         <v>5</v>
@@ -3320,7 +3320,7 @@
         <v>6</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3453,7 +3453,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -3462,27 +3462,30 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>53.13</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>7.9</v>
+      </c>
       <c r="I2">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -3491,22 +3494,25 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>59.38</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>31.25</v>
+      </c>
+      <c r="H3">
+        <v>7.2</v>
       </c>
       <c r="I3">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3514,7 +3520,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>32</v>
@@ -3644,7 +3650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3679,13 +3685,13 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>53</v>
@@ -3693,39 +3699,39 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920307</v>
+        <v>19330051920308</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920308</v>
+        <v>19330051920309</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>53</v>
@@ -3733,79 +3739,79 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920308</v>
+        <v>19330051920311</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920309</v>
+        <v>19330051920311</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920309</v>
+        <v>19330051920316</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920311</v>
+        <v>19330051920325</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>53</v>
@@ -3813,36 +3819,36 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920311</v>
+        <v>19330051920321</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920311</v>
+        <v>19330051920321</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -3853,39 +3859,39 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920312</v>
+        <v>19330051920330</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920312</v>
+        <v>19330051920330</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
         <v>54</v>
@@ -3893,59 +3899,59 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920316</v>
+        <v>19330051920330</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920316</v>
+        <v>19330051920334</v>
       </c>
       <c r="B14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" t="s">
         <v>67</v>
       </c>
-      <c r="C14" t="s">
-        <v>72</v>
-      </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920318</v>
+        <v>19330051920337</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
         <v>53</v>
@@ -3953,39 +3959,39 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920318</v>
+        <v>19330051920338</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920319</v>
+        <v>19330051920342</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
         <v>53</v>
@@ -3993,59 +3999,59 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920319</v>
+        <v>19330051920342</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920323</v>
+        <v>19330051920347</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920323</v>
+        <v>19330051920347</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
         <v>54</v>
@@ -4053,19 +4059,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>19330051920441</v>
+        <v>19330051920347</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
         <v>53</v>
@@ -4073,79 +4079,79 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920441</v>
+        <v>19330051920347</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920325</v>
+        <v>19330051920347</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D23" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="E23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F23" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>19330051920325</v>
+        <v>19330051920345</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D24" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>19330051920321</v>
+        <v>19330051920350</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D25" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
         <v>53</v>
@@ -4153,36 +4159,36 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>19330051920321</v>
+        <v>19330051920350</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D26" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>19330051920321</v>
+        <v>19330051920352</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="E27" t="s">
         <v>6</v>
@@ -4193,39 +4199,39 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>19330051920330</v>
+        <v>19330051920354</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C28" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F28" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>19330051920330</v>
+        <v>19330051920353</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D29" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="E29" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F29" t="s">
         <v>53</v>
@@ -4233,19 +4239,19 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>19330051920330</v>
+        <v>19330051920355</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D30" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F30" t="s">
         <v>54</v>
@@ -4253,981 +4259,61 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>19330051920330</v>
+        <v>19330051920355</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D31" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="E31" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>19330051920332</v>
+        <v>19330051920355</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D32" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="E32" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F32" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>19330051920332</v>
+        <v>19330051920355</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D33" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F33" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>19330051920331</v>
-      </c>
-      <c r="B34" t="s">
-        <v>76</v>
-      </c>
-      <c r="C34" t="s">
-        <v>102</v>
-      </c>
-      <c r="D34" t="s">
-        <v>128</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>19330051920331</v>
-      </c>
-      <c r="B35" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" t="s">
-        <v>102</v>
-      </c>
-      <c r="D35" t="s">
-        <v>128</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>19330051920333</v>
-      </c>
-      <c r="B36" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" t="s">
-        <v>82</v>
-      </c>
-      <c r="D36" t="s">
-        <v>129</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>19330051920333</v>
-      </c>
-      <c r="B37" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" t="s">
-        <v>82</v>
-      </c>
-      <c r="D37" t="s">
-        <v>129</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>19330051920334</v>
-      </c>
-      <c r="B38" t="s">
-        <v>77</v>
-      </c>
-      <c r="C38" t="s">
-        <v>72</v>
-      </c>
-      <c r="D38" t="s">
-        <v>130</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>19330051920334</v>
-      </c>
-      <c r="B39" t="s">
-        <v>77</v>
-      </c>
-      <c r="C39" t="s">
-        <v>72</v>
-      </c>
-      <c r="D39" t="s">
-        <v>130</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>19330051920334</v>
-      </c>
-      <c r="B40" t="s">
-        <v>77</v>
-      </c>
-      <c r="C40" t="s">
-        <v>72</v>
-      </c>
-      <c r="D40" t="s">
-        <v>130</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>19330051920337</v>
-      </c>
-      <c r="B41" t="s">
-        <v>78</v>
-      </c>
-      <c r="C41" t="s">
-        <v>103</v>
-      </c>
-      <c r="D41" t="s">
-        <v>131</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>19330051920337</v>
-      </c>
-      <c r="B42" t="s">
-        <v>78</v>
-      </c>
-      <c r="C42" t="s">
-        <v>103</v>
-      </c>
-      <c r="D42" t="s">
-        <v>131</v>
-      </c>
-      <c r="E42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>19330051920338</v>
-      </c>
-      <c r="B43" t="s">
-        <v>79</v>
-      </c>
-      <c r="C43" t="s">
-        <v>104</v>
-      </c>
-      <c r="D43" t="s">
-        <v>132</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>19330051920338</v>
-      </c>
-      <c r="B44" t="s">
-        <v>79</v>
-      </c>
-      <c r="C44" t="s">
-        <v>104</v>
-      </c>
-      <c r="D44" t="s">
-        <v>132</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>19330051920342</v>
-      </c>
-      <c r="B45" t="s">
-        <v>80</v>
-      </c>
-      <c r="C45" t="s">
-        <v>105</v>
-      </c>
-      <c r="D45" t="s">
-        <v>133</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>19330051920342</v>
-      </c>
-      <c r="B46" t="s">
-        <v>80</v>
-      </c>
-      <c r="C46" t="s">
-        <v>105</v>
-      </c>
-      <c r="D46" t="s">
-        <v>133</v>
-      </c>
-      <c r="E46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>19330051920342</v>
-      </c>
-      <c r="B47" t="s">
-        <v>80</v>
-      </c>
-      <c r="C47" t="s">
-        <v>105</v>
-      </c>
-      <c r="D47" t="s">
-        <v>133</v>
-      </c>
-      <c r="E47" t="s">
-        <v>6</v>
-      </c>
-      <c r="F47" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>19330051920341</v>
-      </c>
-      <c r="B48" t="s">
-        <v>81</v>
-      </c>
-      <c r="C48" t="s">
-        <v>86</v>
-      </c>
-      <c r="D48" t="s">
-        <v>134</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>19330051920341</v>
-      </c>
-      <c r="B49" t="s">
-        <v>81</v>
-      </c>
-      <c r="C49" t="s">
-        <v>86</v>
-      </c>
-      <c r="D49" t="s">
-        <v>134</v>
-      </c>
-      <c r="E49" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>19330051920344</v>
-      </c>
-      <c r="B50" t="s">
-        <v>82</v>
-      </c>
-      <c r="C50" t="s">
-        <v>62</v>
-      </c>
-      <c r="D50" t="s">
-        <v>135</v>
-      </c>
-      <c r="E50" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>19330051920344</v>
-      </c>
-      <c r="B51" t="s">
-        <v>82</v>
-      </c>
-      <c r="C51" t="s">
-        <v>62</v>
-      </c>
-      <c r="D51" t="s">
-        <v>135</v>
-      </c>
-      <c r="E51" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>19330051920347</v>
-      </c>
-      <c r="B52" t="s">
-        <v>83</v>
-      </c>
-      <c r="C52" t="s">
-        <v>106</v>
-      </c>
-      <c r="D52" t="s">
-        <v>136</v>
-      </c>
-      <c r="E52" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>19330051920347</v>
-      </c>
-      <c r="B53" t="s">
-        <v>83</v>
-      </c>
-      <c r="C53" t="s">
-        <v>106</v>
-      </c>
-      <c r="D53" t="s">
-        <v>136</v>
-      </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>19330051920347</v>
-      </c>
-      <c r="B54" t="s">
-        <v>83</v>
-      </c>
-      <c r="C54" t="s">
-        <v>106</v>
-      </c>
-      <c r="D54" t="s">
-        <v>136</v>
-      </c>
-      <c r="E54" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>19330051920347</v>
-      </c>
-      <c r="B55" t="s">
-        <v>83</v>
-      </c>
-      <c r="C55" t="s">
-        <v>106</v>
-      </c>
-      <c r="D55" t="s">
-        <v>136</v>
-      </c>
-      <c r="E55" t="s">
-        <v>5</v>
-      </c>
-      <c r="F55" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>19330051920347</v>
-      </c>
-      <c r="B56" t="s">
-        <v>83</v>
-      </c>
-      <c r="C56" t="s">
-        <v>106</v>
-      </c>
-      <c r="D56" t="s">
-        <v>136</v>
-      </c>
-      <c r="E56" t="s">
-        <v>6</v>
-      </c>
-      <c r="F56" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>19330051920440</v>
-      </c>
-      <c r="B57" t="s">
-        <v>84</v>
-      </c>
-      <c r="C57" t="s">
-        <v>107</v>
-      </c>
-      <c r="D57" t="s">
-        <v>137</v>
-      </c>
-      <c r="E57" t="s">
-        <v>7</v>
-      </c>
-      <c r="F57" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>19330051920440</v>
-      </c>
-      <c r="B58" t="s">
-        <v>84</v>
-      </c>
-      <c r="C58" t="s">
-        <v>107</v>
-      </c>
-      <c r="D58" t="s">
-        <v>137</v>
-      </c>
-      <c r="E58" t="s">
-        <v>10</v>
-      </c>
-      <c r="F58" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>19330051920345</v>
-      </c>
-      <c r="B59" t="s">
-        <v>84</v>
-      </c>
-      <c r="C59" t="s">
-        <v>75</v>
-      </c>
-      <c r="D59" t="s">
-        <v>138</v>
-      </c>
-      <c r="E59" t="s">
-        <v>7</v>
-      </c>
-      <c r="F59" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>19330051920345</v>
-      </c>
-      <c r="B60" t="s">
-        <v>84</v>
-      </c>
-      <c r="C60" t="s">
-        <v>75</v>
-      </c>
-      <c r="D60" t="s">
-        <v>138</v>
-      </c>
-      <c r="E60" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>19330051920346</v>
-      </c>
-      <c r="B61" t="s">
-        <v>84</v>
-      </c>
-      <c r="C61" t="s">
-        <v>108</v>
-      </c>
-      <c r="D61" t="s">
-        <v>139</v>
-      </c>
-      <c r="E61" t="s">
-        <v>7</v>
-      </c>
-      <c r="F61" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>19330051920346</v>
-      </c>
-      <c r="B62" t="s">
-        <v>84</v>
-      </c>
-      <c r="C62" t="s">
-        <v>108</v>
-      </c>
-      <c r="D62" t="s">
-        <v>139</v>
-      </c>
-      <c r="E62" t="s">
-        <v>10</v>
-      </c>
-      <c r="F62" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>19330051920350</v>
-      </c>
-      <c r="B63" t="s">
-        <v>85</v>
-      </c>
-      <c r="C63" t="s">
-        <v>109</v>
-      </c>
-      <c r="D63" t="s">
-        <v>140</v>
-      </c>
-      <c r="E63" t="s">
-        <v>7</v>
-      </c>
-      <c r="F63" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>19330051920350</v>
-      </c>
-      <c r="B64" t="s">
-        <v>85</v>
-      </c>
-      <c r="C64" t="s">
-        <v>109</v>
-      </c>
-      <c r="D64" t="s">
-        <v>140</v>
-      </c>
-      <c r="E64" t="s">
-        <v>10</v>
-      </c>
-      <c r="F64" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>19330051920350</v>
-      </c>
-      <c r="B65" t="s">
-        <v>85</v>
-      </c>
-      <c r="C65" t="s">
-        <v>109</v>
-      </c>
-      <c r="D65" t="s">
-        <v>140</v>
-      </c>
-      <c r="E65" t="s">
-        <v>6</v>
-      </c>
-      <c r="F65" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>19330051920351</v>
-      </c>
-      <c r="B66" t="s">
-        <v>86</v>
-      </c>
-      <c r="C66" t="s">
-        <v>110</v>
-      </c>
-      <c r="D66" t="s">
-        <v>141</v>
-      </c>
-      <c r="E66" t="s">
-        <v>7</v>
-      </c>
-      <c r="F66" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>19330051920351</v>
-      </c>
-      <c r="B67" t="s">
-        <v>86</v>
-      </c>
-      <c r="C67" t="s">
-        <v>110</v>
-      </c>
-      <c r="D67" t="s">
-        <v>141</v>
-      </c>
-      <c r="E67" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>19330051920352</v>
-      </c>
-      <c r="B68" t="s">
-        <v>87</v>
-      </c>
-      <c r="C68" t="s">
-        <v>111</v>
-      </c>
-      <c r="D68" t="s">
-        <v>142</v>
-      </c>
-      <c r="E68" t="s">
-        <v>7</v>
-      </c>
-      <c r="F68" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>19330051920352</v>
-      </c>
-      <c r="B69" t="s">
-        <v>87</v>
-      </c>
-      <c r="C69" t="s">
-        <v>111</v>
-      </c>
-      <c r="D69" t="s">
-        <v>142</v>
-      </c>
-      <c r="E69" t="s">
-        <v>10</v>
-      </c>
-      <c r="F69" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>19330051920352</v>
-      </c>
-      <c r="B70" t="s">
-        <v>87</v>
-      </c>
-      <c r="C70" t="s">
-        <v>111</v>
-      </c>
-      <c r="D70" t="s">
-        <v>142</v>
-      </c>
-      <c r="E70" t="s">
-        <v>6</v>
-      </c>
-      <c r="F70" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>19330051920354</v>
-      </c>
-      <c r="B71" t="s">
-        <v>88</v>
-      </c>
-      <c r="C71" t="s">
-        <v>112</v>
-      </c>
-      <c r="D71" t="s">
-        <v>143</v>
-      </c>
-      <c r="E71" t="s">
-        <v>7</v>
-      </c>
-      <c r="F71" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>19330051920354</v>
-      </c>
-      <c r="B72" t="s">
-        <v>88</v>
-      </c>
-      <c r="C72" t="s">
-        <v>112</v>
-      </c>
-      <c r="D72" t="s">
-        <v>143</v>
-      </c>
-      <c r="E72" t="s">
-        <v>10</v>
-      </c>
-      <c r="F72" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>19330051920354</v>
-      </c>
-      <c r="B73" t="s">
-        <v>88</v>
-      </c>
-      <c r="C73" t="s">
-        <v>112</v>
-      </c>
-      <c r="D73" t="s">
-        <v>143</v>
-      </c>
-      <c r="E73" t="s">
-        <v>6</v>
-      </c>
-      <c r="F73" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>19330051920353</v>
-      </c>
-      <c r="B74" t="s">
-        <v>89</v>
-      </c>
-      <c r="C74" t="s">
-        <v>113</v>
-      </c>
-      <c r="D74" t="s">
-        <v>144</v>
-      </c>
-      <c r="E74" t="s">
-        <v>7</v>
-      </c>
-      <c r="F74" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>19330051920353</v>
-      </c>
-      <c r="B75" t="s">
-        <v>89</v>
-      </c>
-      <c r="C75" t="s">
-        <v>113</v>
-      </c>
-      <c r="D75" t="s">
-        <v>144</v>
-      </c>
-      <c r="E75" t="s">
-        <v>10</v>
-      </c>
-      <c r="F75" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>19330051920355</v>
-      </c>
-      <c r="B76" t="s">
-        <v>88</v>
-      </c>
-      <c r="C76" t="s">
-        <v>88</v>
-      </c>
-      <c r="D76" t="s">
-        <v>145</v>
-      </c>
-      <c r="E76" t="s">
-        <v>7</v>
-      </c>
-      <c r="F76" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>19330051920355</v>
-      </c>
-      <c r="B77" t="s">
-        <v>88</v>
-      </c>
-      <c r="C77" t="s">
-        <v>88</v>
-      </c>
-      <c r="D77" t="s">
-        <v>145</v>
-      </c>
-      <c r="E77" t="s">
-        <v>10</v>
-      </c>
-      <c r="F77" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>19330051920355</v>
-      </c>
-      <c r="B78" t="s">
-        <v>88</v>
-      </c>
-      <c r="C78" t="s">
-        <v>88</v>
-      </c>
-      <c r="D78" t="s">
-        <v>145</v>
-      </c>
-      <c r="E78" t="s">
-        <v>5</v>
-      </c>
-      <c r="F78" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>19330051920355</v>
-      </c>
-      <c r="B79" t="s">
-        <v>88</v>
-      </c>
-      <c r="C79" t="s">
-        <v>88</v>
-      </c>
-      <c r="D79" t="s">
-        <v>145</v>
-      </c>
-      <c r="E79" t="s">
-        <v>6</v>
-      </c>
-      <c r="F79" t="s">
         <v>55</v>
       </c>
     </row>
@@ -5267,13 +4353,13 @@
         <v>19330051920347</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -5281,16 +4367,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920330</v>
+        <v>19330051920355</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -5298,19 +4384,19 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920355</v>
+        <v>19330051920330</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5321,13 +4407,13 @@
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5335,475 +4421,475 @@
         <v>19330051920321</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920334</v>
+        <v>19330051920342</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920342</v>
+        <v>19330051920350</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920350</v>
+        <v>19330051920307</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>140</v>
+        <v>96</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920352</v>
+        <v>19330051920308</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920354</v>
+        <v>19330051920309</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920307</v>
+        <v>19330051920316</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920308</v>
+        <v>19330051920325</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920309</v>
+        <v>19330051920334</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920312</v>
+        <v>19330051920337</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920316</v>
+        <v>19330051920338</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920318</v>
+        <v>19330051920345</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920319</v>
+        <v>19330051920352</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920323</v>
+        <v>19330051920354</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920441</v>
+        <v>19330051920353</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D20" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920325</v>
+        <v>19330051920312</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="D21" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920332</v>
+        <v>19330051920318</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="D22" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920331</v>
+        <v>19330051920319</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="C23" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="D23" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920333</v>
+        <v>19330051920323</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="C24" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="D24" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920337</v>
+        <v>19330051920441</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="D25" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920338</v>
+        <v>19330051920332</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920341</v>
+        <v>19330051920331</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920344</v>
+        <v>19330051920333</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
       <c r="D28" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920440</v>
+        <v>19330051920341</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D29" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920345</v>
+        <v>19330051920344</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="D30" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920346</v>
+        <v>19330051920440</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="D31" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920351</v>
+        <v>19330051920346</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C32" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="D32" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920353</v>
+        <v>19330051920351</v>
       </c>
       <c r="B33" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="C33" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="D33" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5813,7 +4899,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5845,22 +4931,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920307</v>
+        <v>19330051920352</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -5868,68 +4954,68 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920307</v>
+        <v>19330051920352</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>54</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920309</v>
+        <v>19330051920353</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920309</v>
+        <v>19330051920353</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -5937,19 +5023,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920316</v>
+        <v>19330051920307</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
         <v>53</v>
@@ -5960,22 +5046,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920316</v>
+        <v>19330051920309</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -5983,45 +5069,45 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920318</v>
+        <v>19330051920312</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="D8" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920318</v>
+        <v>19330051920316</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -6029,45 +5115,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920319</v>
+        <v>19330051920323</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>118</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920319</v>
+        <v>19330051920325</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -6075,45 +5161,45 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920323</v>
+        <v>19330051920332</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920323</v>
+        <v>19330051920334</v>
       </c>
       <c r="B13" t="s">
         <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -6121,19 +5207,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920441</v>
+        <v>19330051920337</v>
       </c>
       <c r="B14" t="s">
         <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
         <v>53</v>
@@ -6144,530 +5230,24 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920441</v>
+        <v>19330051920345</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>19330051920325</v>
-      </c>
-      <c r="B16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" t="s">
-        <v>99</v>
-      </c>
-      <c r="D16" t="s">
-        <v>124</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>19330051920325</v>
-      </c>
-      <c r="B17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" t="s">
-        <v>99</v>
-      </c>
-      <c r="D17" t="s">
-        <v>124</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>19330051920332</v>
-      </c>
-      <c r="B18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" t="s">
-        <v>127</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>19330051920332</v>
-      </c>
-      <c r="B19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" t="s">
-        <v>72</v>
-      </c>
-      <c r="D19" t="s">
-        <v>127</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>19330051920331</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" t="s">
-        <v>102</v>
-      </c>
-      <c r="D20" t="s">
-        <v>128</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>19330051920331</v>
-      </c>
-      <c r="B21" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" t="s">
-        <v>102</v>
-      </c>
-      <c r="D21" t="s">
-        <v>128</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>19330051920333</v>
-      </c>
-      <c r="B22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" t="s">
-        <v>129</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>53</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>19330051920333</v>
-      </c>
-      <c r="B23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" t="s">
-        <v>82</v>
-      </c>
-      <c r="D23" t="s">
-        <v>129</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>54</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>19330051920337</v>
-      </c>
-      <c r="B24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" t="s">
-        <v>103</v>
-      </c>
-      <c r="D24" t="s">
-        <v>131</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>19330051920337</v>
-      </c>
-      <c r="B25" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" t="s">
-        <v>131</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>54</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>19330051920341</v>
-      </c>
-      <c r="B26" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" t="s">
-        <v>86</v>
-      </c>
-      <c r="D26" t="s">
-        <v>134</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>53</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>19330051920341</v>
-      </c>
-      <c r="B27" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" t="s">
-        <v>86</v>
-      </c>
-      <c r="D27" t="s">
-        <v>134</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>54</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>19330051920344</v>
-      </c>
-      <c r="B28" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" t="s">
-        <v>62</v>
-      </c>
-      <c r="D28" t="s">
-        <v>135</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>53</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>19330051920344</v>
-      </c>
-      <c r="B29" t="s">
-        <v>82</v>
-      </c>
-      <c r="C29" t="s">
-        <v>62</v>
-      </c>
-      <c r="D29" t="s">
-        <v>135</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>54</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>19330051920440</v>
-      </c>
-      <c r="B30" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" t="s">
-        <v>107</v>
-      </c>
-      <c r="D30" t="s">
-        <v>137</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>53</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>19330051920440</v>
-      </c>
-      <c r="B31" t="s">
-        <v>84</v>
-      </c>
-      <c r="C31" t="s">
-        <v>107</v>
-      </c>
-      <c r="D31" t="s">
-        <v>137</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>54</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>19330051920345</v>
-      </c>
-      <c r="B32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" t="s">
-        <v>75</v>
-      </c>
-      <c r="D32" t="s">
-        <v>138</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>19330051920345</v>
-      </c>
-      <c r="B33" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" t="s">
-        <v>75</v>
-      </c>
-      <c r="D33" t="s">
-        <v>138</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>54</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>19330051920346</v>
-      </c>
-      <c r="B34" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" t="s">
-        <v>108</v>
-      </c>
-      <c r="D34" t="s">
-        <v>139</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>53</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>19330051920346</v>
-      </c>
-      <c r="B35" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35" t="s">
-        <v>108</v>
-      </c>
-      <c r="D35" t="s">
-        <v>139</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>54</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>19330051920351</v>
-      </c>
-      <c r="B36" t="s">
-        <v>86</v>
-      </c>
-      <c r="C36" t="s">
-        <v>110</v>
-      </c>
-      <c r="D36" t="s">
-        <v>141</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>53</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>19330051920351</v>
-      </c>
-      <c r="B37" t="s">
-        <v>86</v>
-      </c>
-      <c r="C37" t="s">
-        <v>110</v>
-      </c>
-      <c r="D37" t="s">
-        <v>141</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>54</v>
-      </c>
-      <c r="G37">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/6APV - Estadisticos 20212.xlsx
+++ b/grupos/6APV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -230,232 +230,232 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>XOLIO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>NAVA</t>
+  </si>
+  <si>
+    <t>ARENAS</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>CARLO HUMBERTO</t>
+  </si>
+  <si>
+    <t>JESUS ALBERTO</t>
+  </si>
+  <si>
+    <t>JOSMAR ANTONIO</t>
+  </si>
+  <si>
+    <t>GIOVANNI</t>
+  </si>
+  <si>
+    <t>ARELY</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>VICTOR YAHIR</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>ANDREA YAMILET</t>
+  </si>
+  <si>
+    <t>JESUS ARMANDO</t>
+  </si>
+  <si>
+    <t>GWINETH</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>HERSON ELIAS</t>
+  </si>
+  <si>
+    <t>JOEL</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MANUEL</t>
+  </si>
+  <si>
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
+    <t>PATIÑO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
   </si>
   <si>
     <t>VILLA</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>XOLIO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>NAVA</t>
-  </si>
-  <si>
-    <t>ARENAS</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>AULIS</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
   </si>
   <si>
     <t>BARRAGAN</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>CARLO HUMBERTO</t>
-  </si>
-  <si>
-    <t>JESUS ALBERTO</t>
-  </si>
-  <si>
-    <t>JOSMAR ANTONIO</t>
-  </si>
-  <si>
-    <t>GIOVANNI</t>
-  </si>
-  <si>
-    <t>ARELY</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
+    <t>KEVIN HONAM</t>
+  </si>
+  <si>
+    <t>SAUL ESTEBAN</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>ABRAHAM</t>
+  </si>
+  <si>
+    <t>JESUS MANUEL</t>
+  </si>
+  <si>
+    <t>RUBEN</t>
+  </si>
+  <si>
+    <t>LUZ ABRIL</t>
   </si>
   <si>
     <t>GABRIELA</t>
   </si>
   <si>
-    <t>VICTOR YAHIR</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>ANDREA YAMILET</t>
-  </si>
-  <si>
-    <t>JESUS ARMANDO</t>
-  </si>
-  <si>
-    <t>GWINETH</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
+    <t>CRISTOPHER ENRIQUE</t>
+  </si>
+  <si>
+    <t>CARLOS FERNANDO</t>
+  </si>
+  <si>
+    <t>CIELO IVETTE</t>
+  </si>
+  <si>
+    <t>YOSEF OMAR</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
   </si>
   <si>
     <t>ADAN</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>HERSON ELIAS</t>
-  </si>
-  <si>
-    <t>JOEL</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MANUEL</t>
-  </si>
-  <si>
-    <t>PATIÑO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>AULIS</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>KEVIN HONAM</t>
-  </si>
-  <si>
-    <t>SAUL ESTEBAN</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ABRAHAM</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>RUBEN</t>
-  </si>
-  <si>
-    <t>LUZ ABRIL</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ENRIQUE</t>
-  </si>
-  <si>
-    <t>CARLOS FERNANDO</t>
-  </si>
-  <si>
-    <t>CIELO IVETTE</t>
-  </si>
-  <si>
-    <t>YOSEF OMAR</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
   </si>
 </sst>
 </file>
@@ -2176,7 +2176,7 @@
         <v>8</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -2230,7 +2230,7 @@
         <v>8</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -3100,7 +3100,7 @@
         <v>10</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -3154,7 +3154,7 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V32">
         <v>5</v>
@@ -3558,25 +3558,25 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>68.75</v>
+        <v>75</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>31.25</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3650,7 +3650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3685,10 +3685,10 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -3705,10 +3705,10 @@
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -3725,10 +3725,10 @@
         <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -3745,10 +3745,10 @@
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -3765,10 +3765,10 @@
         <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -3788,7 +3788,7 @@
         <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -3805,10 +3805,10 @@
         <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -3825,10 +3825,10 @@
         <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -3845,10 +3845,10 @@
         <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -3865,10 +3865,10 @@
         <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -3885,10 +3885,10 @@
         <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -3905,10 +3905,10 @@
         <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -3919,36 +3919,36 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920334</v>
+        <v>19330051920337</v>
       </c>
       <c r="B14" t="s">
         <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920337</v>
+        <v>19330051920338</v>
       </c>
       <c r="B15" t="s">
         <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -3959,16 +3959,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920338</v>
+        <v>19330051920342</v>
       </c>
       <c r="B16" t="s">
         <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -3982,39 +3982,39 @@
         <v>19330051920342</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920342</v>
+        <v>19330051920347</v>
       </c>
       <c r="B18" t="s">
         <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -4022,16 +4022,16 @@
         <v>19330051920347</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
         <v>54</v>
@@ -4042,19 +4042,19 @@
         <v>19330051920347</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -4062,19 +4062,19 @@
         <v>19330051920347</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D21" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -4082,53 +4082,53 @@
         <v>19330051920347</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E22" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920347</v>
+        <v>19330051920345</v>
       </c>
       <c r="B23" t="s">
         <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>19330051920345</v>
+        <v>19330051920350</v>
       </c>
       <c r="B24" t="s">
         <v>75</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D24" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -4142,33 +4142,33 @@
         <v>19330051920350</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D25" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F25" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>19330051920350</v>
+        <v>19330051920354</v>
       </c>
       <c r="B26" t="s">
         <v>76</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D26" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E26" t="s">
         <v>6</v>
@@ -4179,56 +4179,56 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>19330051920352</v>
+        <v>19330051920353</v>
       </c>
       <c r="B27" t="s">
         <v>77</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>19330051920354</v>
+        <v>19330051920355</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D28" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E28" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>19330051920353</v>
+        <v>19330051920355</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C29" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="D29" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -4242,19 +4242,19 @@
         <v>19330051920355</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D30" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E30" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F30" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -4262,58 +4262,18 @@
         <v>19330051920355</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D31" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F31" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>19330051920355</v>
-      </c>
-      <c r="B32" t="s">
-        <v>78</v>
-      </c>
-      <c r="C32" t="s">
-        <v>78</v>
-      </c>
-      <c r="D32" t="s">
-        <v>114</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>19330051920355</v>
-      </c>
-      <c r="B33" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33" t="s">
-        <v>78</v>
-      </c>
-      <c r="D33" t="s">
-        <v>114</v>
-      </c>
-      <c r="E33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" t="s">
         <v>55</v>
       </c>
     </row>
@@ -4353,13 +4313,13 @@
         <v>19330051920347</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -4370,13 +4330,13 @@
         <v>19330051920355</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -4390,10 +4350,10 @@
         <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -4407,10 +4367,10 @@
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -4424,10 +4384,10 @@
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -4438,13 +4398,13 @@
         <v>19330051920342</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -4455,13 +4415,13 @@
         <v>19330051920350</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -4475,10 +4435,10 @@
         <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4492,10 +4452,10 @@
         <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -4509,10 +4469,10 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -4529,7 +4489,7 @@
         <v>67</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -4543,10 +4503,10 @@
         <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -4554,16 +4514,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920334</v>
+        <v>19330051920337</v>
       </c>
       <c r="B14" t="s">
         <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -4571,16 +4531,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920337</v>
+        <v>19330051920338</v>
       </c>
       <c r="B15" t="s">
         <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -4588,16 +4548,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920338</v>
+        <v>19330051920345</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -4605,16 +4565,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920345</v>
+        <v>19330051920354</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
         <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -4622,16 +4582,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920352</v>
+        <v>19330051920353</v>
       </c>
       <c r="B18" t="s">
         <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -4639,47 +4599,47 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920354</v>
+        <v>19330051920312</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="D19" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920353</v>
+        <v>19330051920318</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="D20" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920312</v>
+        <v>19330051920319</v>
       </c>
       <c r="B21" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C21" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D21" t="s">
         <v>133</v>
@@ -4690,13 +4650,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920318</v>
+        <v>19330051920323</v>
       </c>
       <c r="B22" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D22" t="s">
         <v>134</v>
@@ -4707,13 +4667,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920319</v>
+        <v>19330051920441</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
         <v>135</v>
@@ -4724,13 +4684,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920323</v>
+        <v>19330051920332</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
         <v>136</v>
@@ -4741,13 +4701,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920441</v>
+        <v>19330051920331</v>
       </c>
       <c r="B25" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C25" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D25" t="s">
         <v>137</v>
@@ -4758,13 +4718,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920332</v>
+        <v>19330051920333</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s">
         <v>138</v>
@@ -4775,13 +4735,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920331</v>
+        <v>19330051920334</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
         <v>139</v>
@@ -4792,13 +4752,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920333</v>
+        <v>19330051920341</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s">
         <v>140</v>
@@ -4809,13 +4769,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920341</v>
+        <v>19330051920344</v>
       </c>
       <c r="B29" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="D29" t="s">
         <v>141</v>
@@ -4826,13 +4786,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920344</v>
+        <v>19330051920440</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="D30" t="s">
         <v>142</v>
@@ -4843,13 +4803,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920440</v>
+        <v>19330051920346</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D31" t="s">
         <v>143</v>
@@ -4860,13 +4820,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920346</v>
+        <v>19330051920351</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D32" t="s">
         <v>144</v>
@@ -4877,13 +4837,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920351</v>
+        <v>19330051920352</v>
       </c>
       <c r="B33" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C33" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D33" t="s">
         <v>145</v>
@@ -4899,7 +4859,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4931,85 +4891,85 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920352</v>
+        <v>19330051920353</v>
       </c>
       <c r="B2" t="s">
         <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920352</v>
+        <v>19330051920353</v>
       </c>
       <c r="B3" t="s">
         <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920353</v>
+        <v>19330051920307</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920353</v>
+        <v>19330051920309</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" t="s">
         <v>95</v>
-      </c>
-      <c r="D5" t="s">
-        <v>113</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5023,39 +4983,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920307</v>
+        <v>19330051920312</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920309</v>
+        <v>19330051920316</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5069,22 +5029,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920312</v>
+        <v>19330051920323</v>
       </c>
       <c r="B8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C8" t="s">
         <v>124</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5092,16 +5052,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920316</v>
+        <v>19330051920325</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -5115,13 +5075,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920323</v>
+        <v>19330051920332</v>
       </c>
       <c r="B10" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
         <v>136</v>
@@ -5138,13 +5098,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920325</v>
+        <v>19330051920337</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
         <v>101</v>
@@ -5161,94 +5121,48 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920332</v>
+        <v>19330051920345</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920334</v>
+        <v>19330051920352</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920337</v>
-      </c>
-      <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" t="s">
-        <v>105</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>19330051920345</v>
-      </c>
-      <c r="B15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6APV - Estadisticos 20212.xlsx
+++ b/grupos/6APV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -179,15 +179,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
@@ -206,6 +206,90 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ARENAS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>JOSMAR ANTONIO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>ANDREA YAMILET</t>
+  </si>
+  <si>
+    <t>JESUS ARMANDO</t>
+  </si>
+  <si>
+    <t>GWINETH</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>JOEL</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
@@ -215,40 +299,46 @@
     <t>ARRIETA</t>
   </si>
   <si>
-    <t>BELLO</t>
+    <t>CARDENAS</t>
   </si>
   <si>
     <t>CERVANTES</t>
   </si>
   <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
+    <t>MANUEL</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
   </si>
   <si>
     <t>MONTIEL</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
+    <t>PATIÑO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VILLA</t>
   </si>
   <si>
     <t>XOLIO</t>
@@ -263,37 +353,40 @@
     <t>NAVA</t>
   </si>
   <si>
-    <t>ARENAS</t>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>AULIS</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
   </si>
   <si>
     <t>GALLARDO</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
+    <t>MORALES</t>
   </si>
   <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
   </si>
   <si>
     <t>RAMOS</t>
@@ -308,154 +401,61 @@
     <t>JESUS ALBERTO</t>
   </si>
   <si>
-    <t>JOSMAR ANTONIO</t>
+    <t>KEVIN HONAM</t>
   </si>
   <si>
     <t>GIOVANNI</t>
   </si>
   <si>
+    <t>SAUL ESTEBAN</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>ABRAHAM</t>
+  </si>
+  <si>
     <t>ARELY</t>
   </si>
   <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
+    <t>JESUS MANUEL</t>
+  </si>
+  <si>
+    <t>RUBEN</t>
+  </si>
+  <si>
+    <t>LUZ ABRIL</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
   </si>
   <si>
     <t>VICTOR YAHIR</t>
   </si>
   <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>ANDREA YAMILET</t>
-  </si>
-  <si>
-    <t>JESUS ARMANDO</t>
-  </si>
-  <si>
-    <t>GWINETH</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
+    <t>CRISTOPHER ENRIQUE</t>
+  </si>
+  <si>
+    <t>CARLOS FERNANDO</t>
+  </si>
+  <si>
+    <t>CIELO IVETTE</t>
+  </si>
+  <si>
+    <t>YOSEF OMAR</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>ADAN</t>
   </si>
   <si>
     <t>HERSON ELIAS</t>
-  </si>
-  <si>
-    <t>JOEL</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MANUEL</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>PATIÑO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>AULIS</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>KEVIN HONAM</t>
-  </si>
-  <si>
-    <t>SAUL ESTEBAN</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ABRAHAM</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>RUBEN</t>
-  </si>
-  <si>
-    <t>LUZ ABRIL</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ENRIQUE</t>
-  </si>
-  <si>
-    <t>CARLOS FERNANDO</t>
-  </si>
-  <si>
-    <t>CIELO IVETTE</t>
-  </si>
-  <si>
-    <t>YOSEF OMAR</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>ADAN</t>
   </si>
 </sst>
 </file>
@@ -956,7 +956,7 @@
         <v>9</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -1010,7 +1010,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1033,7 +1033,7 @@
         <v>6</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H5">
         <v>-1</v>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1110,7 +1110,7 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H6">
         <v>-1</v>
@@ -1164,7 +1164,7 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1341,7 +1341,7 @@
         <v>10</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H9">
         <v>-1</v>
@@ -1395,7 +1395,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1803,7 +1803,7 @@
         <v>10</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H15">
         <v>-1</v>
@@ -1857,7 +1857,7 @@
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2265,7 +2265,7 @@
         <v>9</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H21">
         <v>-1</v>
@@ -2319,7 +2319,7 @@
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2496,7 +2496,7 @@
         <v>5</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H24">
         <v>-1</v>
@@ -2550,7 +2550,7 @@
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -3189,7 +3189,7 @@
         <v>6</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H33">
         <v>-1</v>
@@ -3243,7 +3243,7 @@
         <v>6</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3453,7 +3453,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -3462,62 +3462,62 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>53.13</v>
+        <v>59.38</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>31.25</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="I2">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>46.88</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C3">
         <v>32</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>59.38</v>
+        <v>68.75</v>
       </c>
       <c r="G3">
-        <v>31.25</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>9.380000000000001</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
@@ -3526,30 +3526,30 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>68.75</v>
+        <v>75</v>
       </c>
       <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4">
         <v>25</v>
-      </c>
-      <c r="H4">
-        <v>7.4</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>6.25</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -3558,25 +3558,25 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>75</v>
+        <v>78.13</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>25</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3650,7 +3650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3679,119 +3679,119 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920307</v>
+        <v>19330051920311</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920308</v>
+        <v>19330051920311</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920309</v>
+        <v>19330051920321</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920311</v>
+        <v>19330051920321</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" t="s">
         <v>81</v>
       </c>
-      <c r="D5" t="s">
-        <v>96</v>
-      </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920311</v>
+        <v>19330051920330</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920316</v>
+        <v>19330051920330</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
         <v>53</v>
@@ -3799,119 +3799,119 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920325</v>
+        <v>19330051920330</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" t="s">
         <v>82</v>
       </c>
-      <c r="D8" t="s">
-        <v>98</v>
-      </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920321</v>
+        <v>19330051920338</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" t="s">
         <v>83</v>
       </c>
-      <c r="D9" t="s">
-        <v>99</v>
-      </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920321</v>
+        <v>19330051920342</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920330</v>
+        <v>19330051920347</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920330</v>
+        <v>19330051920347</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920330</v>
+        <v>19330051920347</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
         <v>55</v>
@@ -3919,79 +3919,79 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920337</v>
+        <v>19330051920347</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
         <v>85</v>
       </c>
-      <c r="D14" t="s">
-        <v>101</v>
-      </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920338</v>
+        <v>19330051920347</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920342</v>
+        <v>19330051920345</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920342</v>
+        <v>19330051920350</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" t="s">
         <v>87</v>
       </c>
-      <c r="D17" t="s">
-        <v>103</v>
-      </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
         <v>55</v>
@@ -3999,19 +3999,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920347</v>
+        <v>19330051920350</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
         <v>54</v>
@@ -4019,19 +4019,19 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920347</v>
+        <v>19330051920354</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" t="s">
         <v>88</v>
       </c>
-      <c r="D19" t="s">
-        <v>104</v>
-      </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F19" t="s">
         <v>54</v>
@@ -4039,19 +4039,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920347</v>
+        <v>19330051920355</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
         <v>53</v>
@@ -4059,222 +4059,62 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>19330051920347</v>
+        <v>19330051920355</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D21" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="E21" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920347</v>
+        <v>19330051920355</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920345</v>
+        <v>19330051920355</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" t="s">
         <v>89</v>
       </c>
-      <c r="D23" t="s">
-        <v>105</v>
-      </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F23" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>19330051920350</v>
-      </c>
-      <c r="B24" t="s">
-        <v>75</v>
-      </c>
-      <c r="C24" t="s">
-        <v>90</v>
-      </c>
-      <c r="D24" t="s">
-        <v>106</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>19330051920350</v>
-      </c>
-      <c r="B25" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" t="s">
-        <v>106</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>19330051920354</v>
-      </c>
-      <c r="B26" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" t="s">
-        <v>107</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>19330051920353</v>
-      </c>
-      <c r="B27" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" t="s">
-        <v>92</v>
-      </c>
-      <c r="D27" t="s">
-        <v>108</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>19330051920355</v>
-      </c>
-      <c r="B28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" t="s">
-        <v>76</v>
-      </c>
-      <c r="D28" t="s">
-        <v>109</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>19330051920355</v>
-      </c>
-      <c r="B29" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" t="s">
-        <v>76</v>
-      </c>
-      <c r="D29" t="s">
-        <v>109</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>19330051920355</v>
-      </c>
-      <c r="B30" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" t="s">
-        <v>76</v>
-      </c>
-      <c r="D30" t="s">
-        <v>109</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>19330051920355</v>
-      </c>
-      <c r="B31" t="s">
-        <v>76</v>
-      </c>
-      <c r="C31" t="s">
-        <v>76</v>
-      </c>
-      <c r="D31" t="s">
-        <v>109</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -4313,13 +4153,13 @@
         <v>19330051920347</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -4330,13 +4170,13 @@
         <v>19330051920355</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -4347,13 +4187,13 @@
         <v>19330051920330</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -4364,13 +4204,13 @@
         <v>19330051920311</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -4381,13 +4221,13 @@
         <v>19330051920321</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -4395,16 +4235,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920342</v>
+        <v>19330051920350</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" t="s">
         <v>87</v>
-      </c>
-      <c r="D7" t="s">
-        <v>103</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -4412,33 +4252,33 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920350</v>
+        <v>19330051920338</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920307</v>
+        <v>19330051920342</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4446,16 +4286,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920308</v>
+        <v>19330051920345</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -4463,16 +4303,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920309</v>
+        <v>19330051920354</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -4480,132 +4320,132 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920316</v>
+        <v>19330051920307</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920325</v>
+        <v>19330051920308</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920337</v>
+        <v>19330051920309</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="D14" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920338</v>
+        <v>19330051920312</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920345</v>
+        <v>19330051920316</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920354</v>
+        <v>19330051920318</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920353</v>
+        <v>19330051920319</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920312</v>
+        <v>19330051920323</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="C19" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
         <v>131</v>
@@ -4616,13 +4456,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920318</v>
+        <v>19330051920441</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
         <v>132</v>
@@ -4633,13 +4473,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920319</v>
+        <v>19330051920325</v>
       </c>
       <c r="B21" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
         <v>133</v>
@@ -4650,13 +4490,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920323</v>
+        <v>19330051920332</v>
       </c>
       <c r="B22" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
         <v>134</v>
@@ -4667,13 +4507,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920441</v>
+        <v>19330051920331</v>
       </c>
       <c r="B23" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D23" t="s">
         <v>135</v>
@@ -4684,13 +4524,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920332</v>
+        <v>19330051920333</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
         <v>136</v>
@@ -4701,13 +4541,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920331</v>
+        <v>19330051920334</v>
       </c>
       <c r="B25" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C25" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
         <v>137</v>
@@ -4718,10 +4558,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920333</v>
+        <v>19330051920337</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s">
         <v>118</v>
@@ -4735,13 +4575,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920334</v>
+        <v>19330051920341</v>
       </c>
       <c r="B27" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="D27" t="s">
         <v>139</v>
@@ -4752,13 +4592,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920341</v>
+        <v>19330051920344</v>
       </c>
       <c r="B28" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="D28" t="s">
         <v>140</v>
@@ -4769,13 +4609,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920344</v>
+        <v>19330051920440</v>
       </c>
       <c r="B29" t="s">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s">
         <v>141</v>
@@ -4786,13 +4626,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920440</v>
+        <v>19330051920346</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
         <v>142</v>
@@ -4803,13 +4643,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920346</v>
+        <v>19330051920351</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s">
         <v>143</v>
@@ -4820,13 +4660,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920351</v>
+        <v>19330051920352</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s">
         <v>144</v>
@@ -4837,13 +4677,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920352</v>
+        <v>19330051920353</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="C33" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D33" t="s">
         <v>145</v>
@@ -4859,7 +4699,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4891,22 +4731,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920353</v>
+        <v>19330051920308</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4914,91 +4754,91 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920353</v>
+        <v>19330051920308</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>53</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920307</v>
+        <v>19330051920312</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920309</v>
+        <v>19330051920323</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
         <v>53</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920312</v>
+        <v>19330051920332</v>
       </c>
       <c r="B6" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5006,22 +4846,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920316</v>
+        <v>19330051920345</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -5029,22 +4869,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920323</v>
+        <v>19330051920352</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5052,116 +4892,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920325</v>
+        <v>19330051920353</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
         <v>53</v>
       </c>
       <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920332</v>
-      </c>
-      <c r="B10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" t="s">
-        <v>136</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920337</v>
-      </c>
-      <c r="B11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" t="s">
-        <v>101</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920345</v>
-      </c>
-      <c r="B12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" t="s">
-        <v>105</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19330051920352</v>
-      </c>
-      <c r="B13" t="s">
-        <v>120</v>
-      </c>
-      <c r="C13" t="s">
-        <v>130</v>
-      </c>
-      <c r="D13" t="s">
-        <v>145</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6APV - Estadisticos 20212.xlsx
+++ b/grupos/6APV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -182,15 +182,15 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
     <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
@@ -206,22 +206,94 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>ANDREA YAMILET</t>
+  </si>
+  <si>
+    <t>JESUS ARMANDO</t>
+  </si>
+  <si>
+    <t>JOEL</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>ARRIETA</t>
+  </si>
+  <si>
     <t>BELLO</t>
   </si>
   <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>LOPEZ</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MANUEL</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
   </si>
   <si>
     <t>NAJERA</t>
   </si>
   <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
+    <t>PATIÑO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>SANCHEZ</t>
@@ -230,229 +302,157 @@
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>XOLIO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>NAVA</t>
   </si>
   <si>
     <t>ARENAS</t>
   </si>
   <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>AULIS</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>TZOPITL</t>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
   </si>
   <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
   </si>
   <si>
     <t>BAEZ</t>
   </si>
   <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>CARLO HUMBERTO</t>
+  </si>
+  <si>
+    <t>JESUS ALBERTO</t>
+  </si>
+  <si>
     <t>JOSMAR ANTONIO</t>
   </si>
   <si>
+    <t>KEVIN HONAM</t>
+  </si>
+  <si>
+    <t>GIOVANNI</t>
+  </si>
+  <si>
+    <t>SAUL ESTEBAN</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>ABRAHAM</t>
+  </si>
+  <si>
+    <t>ARELY</t>
+  </si>
+  <si>
     <t>IGNACIO</t>
   </si>
   <si>
-    <t>DIEGO</t>
+    <t>JESUS MANUEL</t>
+  </si>
+  <si>
+    <t>RUBEN</t>
+  </si>
+  <si>
+    <t>LUZ ABRIL</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>VICTOR YAHIR</t>
   </si>
   <si>
     <t>LUIS ENRIQUE</t>
   </si>
   <si>
-    <t>ANDREA YAMILET</t>
-  </si>
-  <si>
-    <t>JESUS ARMANDO</t>
+    <t>CRISTOPHER ENRIQUE</t>
+  </si>
+  <si>
+    <t>CARLOS FERNANDO</t>
+  </si>
+  <si>
+    <t>CIELO IVETTE</t>
   </si>
   <si>
     <t>GWINETH</t>
   </si>
   <si>
+    <t>YOSEF OMAR</t>
+  </si>
+  <si>
     <t>ABIGAIL</t>
   </si>
   <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
     <t>MISAEL</t>
-  </si>
-  <si>
-    <t>JOEL</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>ARRIETA</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MANUEL</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>PATIÑO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>XOLIO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>NAVA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>AULIS</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>CARLO HUMBERTO</t>
-  </si>
-  <si>
-    <t>JESUS ALBERTO</t>
-  </si>
-  <si>
-    <t>KEVIN HONAM</t>
-  </si>
-  <si>
-    <t>GIOVANNI</t>
-  </si>
-  <si>
-    <t>SAUL ESTEBAN</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ABRAHAM</t>
-  </si>
-  <si>
-    <t>ARELY</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>RUBEN</t>
-  </si>
-  <si>
-    <t>LUZ ABRIL</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>VICTOR YAHIR</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ENRIQUE</t>
-  </si>
-  <si>
-    <t>CARLOS FERNANDO</t>
-  </si>
-  <si>
-    <t>CIELO IVETTE</t>
-  </si>
-  <si>
-    <t>YOSEF OMAR</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>ADAN</t>
   </si>
   <si>
     <t>HERSON ELIAS</t>
@@ -959,10 +959,10 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
         <v>-1</v>
@@ -971,10 +971,10 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1007,10 +1007,10 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1036,10 +1036,10 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -1048,10 +1048,10 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1075,7 +1075,7 @@
         <v>7</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>5</v>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1113,10 +1113,10 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -1125,10 +1125,10 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1164,7 +1164,7 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1175,7 +1175,7 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -1187,13 +1187,13 @@
         <v>5</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -1202,10 +1202,10 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1226,10 +1226,10 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -1241,7 +1241,7 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1267,10 +1267,10 @@
         <v>6</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1279,10 +1279,10 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1315,10 +1315,10 @@
         <v>6</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1344,10 +1344,10 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -1356,10 +1356,10 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1395,7 +1395,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1421,10 +1421,10 @@
         <v>7</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
         <v>-1</v>
@@ -1433,10 +1433,10 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1498,10 +1498,10 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
         <v>-1</v>
@@ -1510,10 +1510,10 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1546,10 +1546,10 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1560,7 +1560,7 @@
         <v>8</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D12">
         <v>5</v>
@@ -1572,13 +1572,13 @@
         <v>10</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -1587,10 +1587,10 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1614,7 +1614,7 @@
         <v>8</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>5</v>
@@ -1623,10 +1623,10 @@
         <v>6</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1652,10 +1652,10 @@
         <v>7</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -1664,10 +1664,10 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1688,7 +1688,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1700,10 +1700,10 @@
         <v>7</v>
       </c>
       <c r="X13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1729,10 +1729,10 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
         <v>-1</v>
@@ -1741,10 +1741,10 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1780,7 +1780,7 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1806,10 +1806,10 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>-1</v>
@@ -1818,10 +1818,10 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1857,7 +1857,7 @@
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1868,7 +1868,7 @@
         <v>9</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D16">
         <v>-1</v>
@@ -1883,10 +1883,10 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
         <v>-1</v>
@@ -1895,10 +1895,10 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1919,10 +1919,10 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>-1</v>
@@ -1931,10 +1931,10 @@
         <v>-1</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1960,10 +1960,10 @@
         <v>10</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
         <v>-1</v>
@@ -1972,10 +1972,10 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2037,10 +2037,10 @@
         <v>7</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>-1</v>
@@ -2049,10 +2049,10 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2076,7 +2076,7 @@
         <v>8</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>5</v>
@@ -2088,7 +2088,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2114,10 +2114,10 @@
         <v>7</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -2126,10 +2126,10 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2165,7 +2165,7 @@
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2191,10 +2191,10 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
         <v>-1</v>
@@ -2203,7 +2203,7 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2239,7 +2239,7 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2268,10 +2268,10 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>-1</v>
@@ -2280,10 +2280,10 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2316,10 +2316,10 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2342,13 +2342,13 @@
         <v>6</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>-1</v>
@@ -2357,10 +2357,10 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2384,7 +2384,7 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -2396,7 +2396,7 @@
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2422,10 +2422,10 @@
         <v>10</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -2434,10 +2434,10 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2499,7 +2499,7 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2511,10 +2511,10 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2535,7 +2535,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>-1</v>
@@ -2550,7 +2550,7 @@
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2576,10 +2576,10 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
         <v>-1</v>
@@ -2588,10 +2588,10 @@
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2612,7 +2612,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>10</v>
@@ -2624,7 +2624,7 @@
         <v>8</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2653,10 +2653,10 @@
         <v>7</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
         <v>-1</v>
@@ -2665,10 +2665,10 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2689,7 +2689,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U26">
         <v>10</v>
@@ -2727,13 +2727,13 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
         <v>-1</v>
@@ -2742,10 +2742,10 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2781,7 +2781,7 @@
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2807,10 +2807,10 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
         <v>-1</v>
@@ -2819,10 +2819,10 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2866,7 +2866,7 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C29">
         <v>-1</v>
@@ -2881,10 +2881,10 @@
         <v>5</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -2896,10 +2896,10 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2920,7 +2920,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U29">
         <v>-1</v>
@@ -2935,7 +2935,7 @@
         <v>5</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2946,7 +2946,7 @@
         <v>6</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -2958,13 +2958,13 @@
         <v>5</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
         <v>-1</v>
@@ -2973,10 +2973,10 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3000,7 +3000,7 @@
         <v>6</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>5</v>
@@ -3012,7 +3012,7 @@
         <v>5</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3038,10 +3038,10 @@
         <v>7</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
         <v>-1</v>
@@ -3050,10 +3050,10 @@
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3074,7 +3074,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U31">
         <v>10</v>
@@ -3086,10 +3086,10 @@
         <v>9</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y31">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3115,10 +3115,10 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
         <v>-1</v>
@@ -3127,10 +3127,10 @@
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3154,7 +3154,7 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V32">
         <v>5</v>
@@ -3192,10 +3192,10 @@
         <v>6</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
         <v>-1</v>
@@ -3204,7 +3204,7 @@
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3231,7 +3231,7 @@
         <v>8</v>
       </c>
       <c r="U33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V33">
         <v>7</v>
@@ -3240,7 +3240,7 @@
         <v>5</v>
       </c>
       <c r="X33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y33">
         <v>6</v>
@@ -3254,7 +3254,7 @@
         <v>8</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D34">
         <v>5</v>
@@ -3269,10 +3269,10 @@
         <v>6</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J34">
         <v>-1</v>
@@ -3281,10 +3281,10 @@
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3308,7 +3308,7 @@
         <v>8</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V34">
         <v>5</v>
@@ -3317,10 +3317,10 @@
         <v>5</v>
       </c>
       <c r="X34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y34">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3328,7 +3328,7 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C35">
         <v>-1</v>
@@ -3343,10 +3343,10 @@
         <v>5</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -3358,10 +3358,10 @@
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3382,7 +3382,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U35">
         <v>-1</v>
@@ -3397,7 +3397,7 @@
         <v>5</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3485,71 +3485,71 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3">
         <v>32</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>68.75</v>
+        <v>59.38</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>40.63</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C4">
         <v>32</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>75</v>
+        <v>68.75</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>9.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>25</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -3558,30 +3558,30 @@
         <v>32</v>
       </c>
       <c r="D5">
+        <v>24</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>75</v>
+      </c>
+      <c r="G5">
         <v>25</v>
       </c>
-      <c r="E5">
+      <c r="H5">
+        <v>7.4</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>78.13</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>7.3</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>21.88</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -3590,25 +3590,25 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>81.25</v>
+        <v>90.63</v>
       </c>
       <c r="G6">
-        <v>18.75</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3622,25 +3622,25 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3650,7 +3650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3679,99 +3679,99 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920311</v>
+        <v>19330051920330</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920311</v>
+        <v>19330051920330</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920321</v>
+        <v>19330051920342</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920321</v>
+        <v>19330051920347</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920330</v>
+        <v>19330051920347</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
         <v>53</v>
@@ -3779,342 +3779,62 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920330</v>
+        <v>19330051920347</v>
       </c>
       <c r="B7" t="s">
         <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920330</v>
+        <v>19330051920355</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920338</v>
+        <v>19330051920355</v>
       </c>
       <c r="B9" t="s">
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>19330051920342</v>
-      </c>
-      <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920347</v>
-      </c>
-      <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" t="s">
-        <v>85</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920347</v>
-      </c>
-      <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>19330051920347</v>
-      </c>
-      <c r="B13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920347</v>
-      </c>
-      <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" t="s">
-        <v>85</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>19330051920347</v>
-      </c>
-      <c r="B15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" t="s">
-        <v>85</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>19330051920345</v>
-      </c>
-      <c r="B16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" t="s">
-        <v>86</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>19330051920350</v>
-      </c>
-      <c r="B17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" t="s">
-        <v>87</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>19330051920350</v>
-      </c>
-      <c r="B18" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D18" t="s">
-        <v>87</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>19330051920354</v>
-      </c>
-      <c r="B19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" t="s">
-        <v>88</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>19330051920355</v>
-      </c>
-      <c r="B20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" t="s">
-        <v>89</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>19330051920355</v>
-      </c>
-      <c r="B21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" t="s">
-        <v>89</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>19330051920355</v>
-      </c>
-      <c r="B22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>19330051920355</v>
-      </c>
-      <c r="B23" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" t="s">
-        <v>89</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -4153,180 +3873,180 @@
         <v>19330051920347</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920355</v>
+        <v>19330051920330</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920330</v>
+        <v>19330051920355</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920311</v>
+        <v>19330051920342</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920321</v>
+        <v>19330051920307</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920350</v>
+        <v>19330051920308</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920338</v>
+        <v>19330051920309</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920342</v>
+        <v>19330051920311</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920345</v>
+        <v>19330051920312</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920354</v>
+        <v>19330051920316</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920307</v>
+        <v>19330051920318</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
         <v>124</v>
@@ -4337,13 +4057,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920308</v>
+        <v>19330051920319</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
         <v>125</v>
@@ -4354,13 +4074,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920309</v>
+        <v>19330051920323</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
         <v>126</v>
@@ -4371,13 +4091,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920312</v>
+        <v>19330051920441</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
         <v>127</v>
@@ -4388,13 +4108,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920316</v>
+        <v>19330051920325</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
         <v>128</v>
@@ -4405,13 +4125,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920318</v>
+        <v>19330051920321</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
         <v>129</v>
@@ -4422,13 +4142,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920319</v>
+        <v>19330051920332</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
         <v>130</v>
@@ -4439,13 +4159,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920323</v>
+        <v>19330051920331</v>
       </c>
       <c r="B19" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D19" t="s">
         <v>131</v>
@@ -4456,13 +4176,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920441</v>
+        <v>19330051920333</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="D20" t="s">
         <v>132</v>
@@ -4473,13 +4193,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920325</v>
+        <v>19330051920334</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="D21" t="s">
         <v>133</v>
@@ -4490,13 +4210,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920332</v>
+        <v>19330051920337</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
         <v>134</v>
@@ -4507,13 +4227,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920331</v>
+        <v>19330051920338</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D23" t="s">
         <v>135</v>
@@ -4524,13 +4244,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920333</v>
+        <v>19330051920341</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D24" t="s">
         <v>136</v>
@@ -4541,13 +4261,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920334</v>
+        <v>19330051920344</v>
       </c>
       <c r="B25" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s">
         <v>137</v>
@@ -4558,13 +4278,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920337</v>
+        <v>19330051920440</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s">
         <v>138</v>
@@ -4575,13 +4295,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920341</v>
+        <v>19330051920345</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
         <v>139</v>
@@ -4592,13 +4312,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920344</v>
+        <v>19330051920346</v>
       </c>
       <c r="B28" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="D28" t="s">
         <v>140</v>
@@ -4609,13 +4329,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920440</v>
+        <v>19330051920350</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D29" t="s">
         <v>141</v>
@@ -4626,13 +4346,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920346</v>
+        <v>19330051920351</v>
       </c>
       <c r="B30" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D30" t="s">
         <v>142</v>
@@ -4643,13 +4363,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920351</v>
+        <v>19330051920352</v>
       </c>
       <c r="B31" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D31" t="s">
         <v>143</v>
@@ -4660,13 +4380,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920352</v>
+        <v>19330051920354</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D32" t="s">
         <v>144</v>
@@ -4680,10 +4400,10 @@
         <v>19330051920353</v>
       </c>
       <c r="B33" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D33" t="s">
         <v>145</v>
@@ -4699,7 +4419,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4731,16 +4451,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920308</v>
+        <v>19330051920330</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -4749,21 +4469,21 @@
         <v>53</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920308</v>
+        <v>19330051920330</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4772,27 +4492,27 @@
         <v>53</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920312</v>
+        <v>19330051920353</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4800,22 +4520,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920323</v>
+        <v>19330051920353</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4823,22 +4543,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920332</v>
+        <v>19330051920307</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4846,45 +4566,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920345</v>
+        <v>19330051920312</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920352</v>
+        <v>19330051920316</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4892,24 +4612,162 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920353</v>
+        <v>19330051920323</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
         <v>53</v>
       </c>
       <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>19330051920325</v>
+      </c>
+      <c r="B10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>19330051920321</v>
+      </c>
+      <c r="B11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>19330051920332</v>
+      </c>
+      <c r="B12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" t="s">
+        <v>130</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>19330051920334</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" t="s">
+        <v>133</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>19330051920337</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" t="s">
+        <v>134</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>19330051920352</v>
+      </c>
+      <c r="B15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" t="s">
+        <v>143</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6APV - Estadisticos 20212.xlsx
+++ b/grupos/6APV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -179,12 +179,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
@@ -206,208 +206,208 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>ANDREA YAMILET</t>
+  </si>
+  <si>
+    <t>JESUS ARMANDO</t>
+  </si>
+  <si>
+    <t>JOEL</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>ARRIETA</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MANUEL</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>PATIÑO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>XOLIO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>NAVA</t>
+  </si>
+  <si>
+    <t>ARENAS</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>AULIS</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>TZOPITL</t>
   </si>
   <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>CARLO HUMBERTO</t>
+  </si>
+  <si>
+    <t>JESUS ALBERTO</t>
+  </si>
+  <si>
+    <t>JOSMAR ANTONIO</t>
+  </si>
+  <si>
+    <t>KEVIN HONAM</t>
+  </si>
+  <si>
+    <t>GIOVANNI</t>
+  </si>
+  <si>
+    <t>SAUL ESTEBAN</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>ABRAHAM</t>
+  </si>
+  <si>
+    <t>ARELY</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
   </si>
   <si>
     <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ANDREA YAMILET</t>
-  </si>
-  <si>
-    <t>JESUS ARMANDO</t>
-  </si>
-  <si>
-    <t>JOEL</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>ARRIETA</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MANUEL</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>PATIÑO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>XOLIO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>NAVA</t>
-  </si>
-  <si>
-    <t>ARENAS</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>AULIS</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>CARLO HUMBERTO</t>
-  </si>
-  <si>
-    <t>JESUS ALBERTO</t>
-  </si>
-  <si>
-    <t>JOSMAR ANTONIO</t>
-  </si>
-  <si>
-    <t>KEVIN HONAM</t>
-  </si>
-  <si>
-    <t>GIOVANNI</t>
-  </si>
-  <si>
-    <t>SAUL ESTEBAN</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ABRAHAM</t>
-  </si>
-  <si>
-    <t>ARELY</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
   </si>
   <si>
     <t>JESUS MANUEL</t>
@@ -965,10 +965,10 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>6</v>
@@ -1001,10 +1001,10 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>8</v>
@@ -1119,10 +1119,10 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -1155,7 +1155,7 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -1196,10 +1196,10 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>6</v>
@@ -1273,10 +1273,10 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
         <v>7</v>
@@ -1309,7 +1309,7 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>6</v>
@@ -1350,10 +1350,10 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -1389,7 +1389,7 @@
         <v>10</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -1427,10 +1427,10 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -1504,10 +1504,10 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>7</v>
@@ -1581,10 +1581,10 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>5</v>
@@ -1620,7 +1620,7 @@
         <v>5</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -1658,10 +1658,10 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>8</v>
@@ -1735,10 +1735,10 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>6</v>
@@ -1812,10 +1812,10 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
         <v>9</v>
@@ -1871,10 +1871,10 @@
         <v>8</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F16">
         <v>7</v>
@@ -1889,10 +1889,10 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>5</v>
@@ -1925,10 +1925,10 @@
         <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X16">
         <v>6</v>
@@ -1966,10 +1966,10 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
         <v>10</v>
@@ -2043,10 +2043,10 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
         <v>7</v>
@@ -2079,7 +2079,7 @@
         <v>9</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -2120,10 +2120,10 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
         <v>10</v>
@@ -2197,10 +2197,10 @@
         <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L20">
         <v>5</v>
@@ -2233,10 +2233,10 @@
         <v>6</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X20">
         <v>5</v>
@@ -2274,10 +2274,10 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -2313,7 +2313,7 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2351,10 +2351,10 @@
         <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
         <v>6</v>
@@ -2390,7 +2390,7 @@
         <v>5</v>
       </c>
       <c r="W22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2428,10 +2428,10 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -2505,10 +2505,10 @@
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>5</v>
@@ -2582,10 +2582,10 @@
         <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
         <v>9</v>
@@ -2659,10 +2659,10 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>8</v>
@@ -2736,10 +2736,10 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
         <v>9</v>
@@ -2772,7 +2772,7 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>9</v>
@@ -2813,10 +2813,10 @@
         <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
         <v>9</v>
@@ -2849,7 +2849,7 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W28">
         <v>10</v>
@@ -3044,10 +3044,10 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
         <v>7</v>
@@ -3080,7 +3080,7 @@
         <v>10</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>9</v>
@@ -3121,10 +3121,10 @@
         <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
         <v>6</v>
@@ -3160,7 +3160,7 @@
         <v>5</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X32">
         <v>7</v>
@@ -3275,10 +3275,10 @@
         <v>7</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L34">
         <v>5</v>
@@ -3453,7 +3453,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -3465,27 +3465,27 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2">
         <v>59.38</v>
       </c>
       <c r="G2">
-        <v>31.25</v>
+        <v>40.63</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -3494,25 +3494,25 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>59.38</v>
+        <v>62.5</v>
       </c>
       <c r="G3">
-        <v>40.63</v>
+        <v>31.25</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3520,31 +3520,31 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>32</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>68.75</v>
+        <v>65.63</v>
       </c>
       <c r="G4">
-        <v>25</v>
+        <v>31.25</v>
       </c>
       <c r="H4">
         <v>7.4</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>6.25</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3650,7 +3650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3679,62 +3679,62 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920330</v>
+        <v>19330051920342</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920330</v>
+        <v>19330051920347</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
         <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920342</v>
+        <v>19330051920347</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3742,98 +3742,58 @@
         <v>19330051920347</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" t="s">
         <v>68</v>
       </c>
-      <c r="D5" t="s">
-        <v>71</v>
-      </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920347</v>
+        <v>19330051920355</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920347</v>
+        <v>19330051920355</v>
       </c>
       <c r="B7" t="s">
         <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920355</v>
-      </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330051920355</v>
-      </c>
-      <c r="B9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
         <v>56</v>
       </c>
     </row>
@@ -3873,13 +3833,13 @@
         <v>19330051920347</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" t="s">
         <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>71</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -3887,13 +3847,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920330</v>
+        <v>19330051920355</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
         <v>69</v>
@@ -3904,47 +3864,47 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920355</v>
+        <v>19330051920342</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
         <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920342</v>
+        <v>19330051920307</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920307</v>
+        <v>19330051920308</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
         <v>118</v>
@@ -3955,13 +3915,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920308</v>
+        <v>19330051920309</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
         <v>119</v>
@@ -3972,13 +3932,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920309</v>
+        <v>19330051920311</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
         <v>120</v>
@@ -3989,13 +3949,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920311</v>
+        <v>19330051920312</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
         <v>121</v>
@@ -4006,13 +3966,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920312</v>
+        <v>19330051920316</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
         <v>122</v>
@@ -4023,13 +3983,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920316</v>
+        <v>19330051920318</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
         <v>123</v>
@@ -4040,13 +4000,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920318</v>
+        <v>19330051920319</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
         <v>124</v>
@@ -4057,13 +4017,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920319</v>
+        <v>19330051920323</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D13" t="s">
         <v>125</v>
@@ -4074,13 +4034,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920323</v>
+        <v>19330051920441</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
         <v>126</v>
@@ -4091,13 +4051,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920441</v>
+        <v>19330051920325</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
         <v>127</v>
@@ -4108,13 +4068,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920325</v>
+        <v>19330051920321</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
         <v>128</v>
@@ -4125,13 +4085,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920321</v>
+        <v>19330051920330</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
         <v>129</v>
@@ -4145,10 +4105,10 @@
         <v>19330051920332</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
         <v>130</v>
@@ -4162,10 +4122,10 @@
         <v>19330051920331</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
         <v>131</v>
@@ -4179,10 +4139,10 @@
         <v>19330051920333</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
         <v>132</v>
@@ -4196,10 +4156,10 @@
         <v>19330051920334</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D21" t="s">
         <v>133</v>
@@ -4213,10 +4173,10 @@
         <v>19330051920337</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
         <v>134</v>
@@ -4230,10 +4190,10 @@
         <v>19330051920338</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
         <v>135</v>
@@ -4247,10 +4207,10 @@
         <v>19330051920341</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
         <v>136</v>
@@ -4264,10 +4224,10 @@
         <v>19330051920344</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D25" t="s">
         <v>137</v>
@@ -4281,10 +4241,10 @@
         <v>19330051920440</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s">
         <v>138</v>
@@ -4298,10 +4258,10 @@
         <v>19330051920345</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D27" t="s">
         <v>139</v>
@@ -4315,10 +4275,10 @@
         <v>19330051920346</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
         <v>140</v>
@@ -4332,10 +4292,10 @@
         <v>19330051920350</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D29" t="s">
         <v>141</v>
@@ -4349,10 +4309,10 @@
         <v>19330051920351</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D30" t="s">
         <v>142</v>
@@ -4366,10 +4326,10 @@
         <v>19330051920352</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D31" t="s">
         <v>143</v>
@@ -4383,10 +4343,10 @@
         <v>19330051920354</v>
       </c>
       <c r="B32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C32" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D32" t="s">
         <v>144</v>
@@ -4400,10 +4360,10 @@
         <v>19330051920353</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D33" t="s">
         <v>145</v>
@@ -4451,68 +4411,68 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920330</v>
+        <v>19330051920321</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920330</v>
+        <v>19330051920321</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920353</v>
+        <v>19330051920338</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4520,22 +4480,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920353</v>
+        <v>19330051920338</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4543,19 +4503,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920307</v>
+        <v>19330051920353</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
         <v>54</v>
@@ -4566,22 +4526,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920312</v>
+        <v>19330051920353</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4589,22 +4549,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920316</v>
+        <v>19330051920307</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4612,19 +4572,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920323</v>
+        <v>19330051920312</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>53</v>
@@ -4635,22 +4595,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920325</v>
+        <v>19330051920316</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4658,22 +4618,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920321</v>
+        <v>19330051920323</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4681,19 +4641,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920332</v>
+        <v>19330051920325</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
         <v>53</v>
@@ -4704,22 +4664,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920334</v>
+        <v>19330051920330</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="D13" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -4730,10 +4690,10 @@
         <v>19330051920337</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
         <v>134</v>
@@ -4742,7 +4702,7 @@
         <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -4753,10 +4713,10 @@
         <v>19330051920352</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D15" t="s">
         <v>143</v>
@@ -4765,7 +4725,7 @@
         <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G15">
         <v>5</v>

--- a/grupos/6APV - Estadisticos 20212.xlsx
+++ b/grupos/6APV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -977,7 +977,7 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -989,7 +989,7 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -1054,7 +1054,7 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -1066,13 +1066,13 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -1084,7 +1084,7 @@
         <v>5</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1131,7 +1131,7 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1143,13 +1143,13 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>10</v>
@@ -1161,7 +1161,7 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>8</v>
@@ -1208,7 +1208,7 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1220,7 +1220,7 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1238,7 +1238,7 @@
         <v>5</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -1285,7 +1285,7 @@
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1297,13 +1297,13 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>10</v>
@@ -1315,7 +1315,7 @@
         <v>6</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>5</v>
@@ -1362,7 +1362,7 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1374,7 +1374,7 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1439,7 +1439,7 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1451,7 +1451,7 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1516,7 +1516,7 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1528,13 +1528,13 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>10</v>
@@ -1593,7 +1593,7 @@
         <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1605,13 +1605,13 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>9</v>
@@ -1623,7 +1623,7 @@
         <v>5</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -1670,7 +1670,7 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1682,13 +1682,13 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1700,7 +1700,7 @@
         <v>7</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1747,7 +1747,7 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1759,7 +1759,7 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1824,7 +1824,7 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1836,7 +1836,7 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1854,7 +1854,7 @@
         <v>10</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -1901,7 +1901,7 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -1913,13 +1913,13 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>9</v>
@@ -1931,7 +1931,7 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>9</v>
@@ -1978,7 +1978,7 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -1990,7 +1990,7 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -2055,7 +2055,7 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2067,13 +2067,13 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>9</v>
@@ -2132,7 +2132,7 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2144,7 +2144,7 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2209,7 +2209,7 @@
         <v>-1</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2221,13 +2221,13 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>6</v>
@@ -2286,7 +2286,7 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2298,13 +2298,13 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>10</v>
@@ -2363,7 +2363,7 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2375,7 +2375,7 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2393,7 +2393,7 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2440,7 +2440,7 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2452,7 +2452,7 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2517,7 +2517,7 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2529,13 +2529,13 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S24">
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U24">
         <v>-1</v>
@@ -2594,7 +2594,7 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2606,7 +2606,7 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2671,7 +2671,7 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2683,7 +2683,7 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2701,7 +2701,7 @@
         <v>8</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>7</v>
@@ -2748,7 +2748,7 @@
         <v>7</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -2760,13 +2760,13 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S27">
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U27">
         <v>10</v>
@@ -2778,7 +2778,7 @@
         <v>9</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2825,7 +2825,7 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -2837,7 +2837,7 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -2902,7 +2902,7 @@
         <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -2914,13 +2914,13 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S29">
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U29">
         <v>-1</v>
@@ -2979,7 +2979,7 @@
         <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -2991,13 +2991,13 @@
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U30">
         <v>8</v>
@@ -3056,7 +3056,7 @@
         <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -3068,7 +3068,7 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3133,7 +3133,7 @@
         <v>7</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -3145,13 +3145,13 @@
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U32">
         <v>8</v>
@@ -3210,7 +3210,7 @@
         <v>-1</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -3222,13 +3222,13 @@
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S33">
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>8</v>
@@ -3287,7 +3287,7 @@
         <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -3299,13 +3299,13 @@
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U34">
         <v>7</v>
@@ -3317,7 +3317,7 @@
         <v>5</v>
       </c>
       <c r="X34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y34">
         <v>5</v>
@@ -3364,7 +3364,7 @@
         <v>5</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O35">
         <v>-1</v>
@@ -3376,13 +3376,13 @@
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S35">
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U35">
         <v>-1</v>
@@ -3622,19 +3622,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4379,7 +4379,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4411,16 +4411,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920321</v>
+        <v>19330051920338</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -4434,22 +4434,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920321</v>
+        <v>19330051920338</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4457,19 +4457,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920338</v>
+        <v>19330051920353</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>54</v>
@@ -4480,22 +4480,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920338</v>
+        <v>19330051920353</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4503,22 +4503,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920353</v>
+        <v>19330051920307</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4526,22 +4526,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920353</v>
+        <v>19330051920312</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4549,16 +4549,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920307</v>
+        <v>19330051920316</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -4572,22 +4572,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920312</v>
+        <v>19330051920323</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4595,16 +4595,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920316</v>
+        <v>19330051920325</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -4618,19 +4618,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920323</v>
+        <v>19330051920330</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
         <v>54</v>
@@ -4641,16 +4641,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920325</v>
+        <v>19330051920337</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -4664,70 +4664,24 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920330</v>
+        <v>19330051920352</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D13" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
         <v>54</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920337</v>
-      </c>
-      <c r="B14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" t="s">
-        <v>108</v>
-      </c>
-      <c r="D14" t="s">
-        <v>134</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>19330051920352</v>
-      </c>
-      <c r="B15" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" t="s">
-        <v>114</v>
-      </c>
-      <c r="D15" t="s">
-        <v>143</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6APV - Estadisticos 20212.xlsx
+++ b/grupos/6APV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -188,12 +188,12 @@
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
+    <t>Sánchez Sánchez Miguel</t>
+  </si>
+  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
-    <t>Sánchez Sánchez Miguel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -206,226 +206,226 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>JESUS ARMANDO</t>
+  </si>
+  <si>
+    <t>JOEL</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>ARRIETA</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MANUEL</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
     <t>PAZ</t>
   </si>
   <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
+    <t>PATIÑO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>XOLIO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>NAVA</t>
+  </si>
+  <si>
+    <t>ARENAS</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>AULIS</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
   </si>
   <si>
     <t>MONTERROSAS</t>
   </si>
   <si>
-    <t>CAMPOS</t>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>CARLO HUMBERTO</t>
+  </si>
+  <si>
+    <t>JESUS ALBERTO</t>
+  </si>
+  <si>
+    <t>JOSMAR ANTONIO</t>
+  </si>
+  <si>
+    <t>KEVIN HONAM</t>
+  </si>
+  <si>
+    <t>GIOVANNI</t>
+  </si>
+  <si>
+    <t>SAUL ESTEBAN</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>ABRAHAM</t>
+  </si>
+  <si>
+    <t>ARELY</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>JESUS MANUEL</t>
+  </si>
+  <si>
+    <t>RUBEN</t>
+  </si>
+  <si>
+    <t>LUZ ABRIL</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>VICTOR YAHIR</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
   </si>
   <si>
     <t>ANDREA YAMILET</t>
-  </si>
-  <si>
-    <t>JESUS ARMANDO</t>
-  </si>
-  <si>
-    <t>JOEL</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>ARRIETA</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MANUEL</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>PATIÑO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>XOLIO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>NAVA</t>
-  </si>
-  <si>
-    <t>ARENAS</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>AULIS</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>CARLO HUMBERTO</t>
-  </si>
-  <si>
-    <t>JESUS ALBERTO</t>
-  </si>
-  <si>
-    <t>JOSMAR ANTONIO</t>
-  </si>
-  <si>
-    <t>KEVIN HONAM</t>
-  </si>
-  <si>
-    <t>GIOVANNI</t>
-  </si>
-  <si>
-    <t>SAUL ESTEBAN</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ABRAHAM</t>
-  </si>
-  <si>
-    <t>ARELY</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>RUBEN</t>
-  </si>
-  <si>
-    <t>LUZ ABRIL</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>VICTOR YAHIR</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
   </si>
   <si>
     <t>CRISTOPHER ENRIQUE</t>
@@ -980,7 +980,7 @@
         <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1057,7 +1057,7 @@
         <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1075,7 +1075,7 @@
         <v>6</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>5</v>
@@ -1134,7 +1134,7 @@
         <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1152,7 +1152,7 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -1211,7 +1211,7 @@
         <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1288,7 +1288,7 @@
         <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1306,7 +1306,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>7</v>
@@ -1365,7 +1365,7 @@
         <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1442,7 +1442,7 @@
         <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1519,7 +1519,7 @@
         <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1596,7 +1596,7 @@
         <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1614,7 +1614,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>5</v>
@@ -1673,7 +1673,7 @@
         <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1691,7 +1691,7 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -1750,7 +1750,7 @@
         <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1827,7 +1827,7 @@
         <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1904,7 +1904,7 @@
         <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1981,7 +1981,7 @@
         <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2058,7 +2058,7 @@
         <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2135,7 +2135,7 @@
         <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2212,7 +2212,7 @@
         <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2289,7 +2289,7 @@
         <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2366,7 +2366,7 @@
         <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2384,7 +2384,7 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -2443,7 +2443,7 @@
         <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2484,7 +2484,7 @@
         <v>8</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D24">
         <v>5</v>
@@ -2502,7 +2502,7 @@
         <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
         <v>5</v>
@@ -2520,7 +2520,7 @@
         <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2538,7 +2538,7 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V24">
         <v>5</v>
@@ -2597,7 +2597,7 @@
         <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2674,7 +2674,7 @@
         <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2751,7 +2751,7 @@
         <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2828,7 +2828,7 @@
         <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -2869,7 +2869,7 @@
         <v>6</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D29">
         <v>-1</v>
@@ -2887,7 +2887,7 @@
         <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
         <v>-1</v>
@@ -2905,7 +2905,7 @@
         <v>5</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -2923,7 +2923,7 @@
         <v>5</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V29">
         <v>-1</v>
@@ -2982,7 +2982,7 @@
         <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3059,7 +3059,7 @@
         <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3136,7 +3136,7 @@
         <v>6</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3154,7 +3154,7 @@
         <v>8</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V32">
         <v>5</v>
@@ -3213,7 +3213,7 @@
         <v>6</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3231,7 +3231,7 @@
         <v>7</v>
       </c>
       <c r="U33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V33">
         <v>7</v>
@@ -3290,7 +3290,7 @@
         <v>6</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3308,7 +3308,7 @@
         <v>7</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V34">
         <v>5</v>
@@ -3331,7 +3331,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D35">
         <v>-1</v>
@@ -3349,7 +3349,7 @@
         <v>6</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J35">
         <v>-1</v>
@@ -3367,7 +3367,7 @@
         <v>5</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3385,7 +3385,7 @@
         <v>5</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V35">
         <v>-1</v>
@@ -3581,7 +3581,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -3590,30 +3590,30 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>93.75</v>
+      </c>
+      <c r="G6">
+        <v>6.25</v>
+      </c>
+      <c r="H6">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>90.63</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
@@ -3634,7 +3634,7 @@
         <v>6.25</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3650,7 +3650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3679,22 +3679,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920342</v>
+        <v>19330051920347</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" t="s">
         <v>65</v>
       </c>
-      <c r="D2" t="s">
-        <v>67</v>
-      </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3702,16 +3702,16 @@
         <v>19330051920347</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>54</v>
@@ -3719,82 +3719,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920347</v>
+        <v>19330051920355</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
       </c>
       <c r="C4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" t="s">
         <v>66</v>
-      </c>
-      <c r="D4" t="s">
-        <v>68</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920347</v>
-      </c>
-      <c r="B5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920355</v>
-      </c>
-      <c r="B6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920355</v>
-      </c>
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -3833,16 +3773,16 @@
         <v>19330051920347</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3850,44 +3790,44 @@
         <v>19330051920355</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920342</v>
+        <v>19330051920307</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920307</v>
+        <v>19330051920308</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
         <v>117</v>
@@ -3898,13 +3838,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920308</v>
+        <v>19330051920309</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
         <v>118</v>
@@ -3915,13 +3855,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920309</v>
+        <v>19330051920311</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
         <v>119</v>
@@ -3932,13 +3872,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920311</v>
+        <v>19330051920312</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
         <v>120</v>
@@ -3949,13 +3889,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920312</v>
+        <v>19330051920316</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
         <v>121</v>
@@ -3966,13 +3906,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920316</v>
+        <v>19330051920318</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
         <v>122</v>
@@ -3983,13 +3923,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920318</v>
+        <v>19330051920319</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
         <v>123</v>
@@ -4000,13 +3940,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920319</v>
+        <v>19330051920323</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
         <v>124</v>
@@ -4017,13 +3957,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920323</v>
+        <v>19330051920441</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
         <v>125</v>
@@ -4034,13 +3974,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920441</v>
+        <v>19330051920325</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
         <v>126</v>
@@ -4051,13 +3991,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920325</v>
+        <v>19330051920321</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
         <v>127</v>
@@ -4068,13 +4008,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920321</v>
+        <v>19330051920330</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
         <v>128</v>
@@ -4085,13 +4025,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920330</v>
+        <v>19330051920332</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
         <v>129</v>
@@ -4102,13 +4042,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920332</v>
+        <v>19330051920331</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
         <v>130</v>
@@ -4119,13 +4059,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920331</v>
+        <v>19330051920333</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s">
         <v>131</v>
@@ -4136,13 +4076,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920333</v>
+        <v>19330051920334</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
         <v>132</v>
@@ -4153,13 +4093,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920334</v>
+        <v>19330051920337</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="D21" t="s">
         <v>133</v>
@@ -4170,13 +4110,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920337</v>
+        <v>19330051920338</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
         <v>134</v>
@@ -4187,13 +4127,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920338</v>
+        <v>19330051920342</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
         <v>135</v>
@@ -4207,10 +4147,10 @@
         <v>19330051920341</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D24" t="s">
         <v>136</v>
@@ -4224,10 +4164,10 @@
         <v>19330051920344</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s">
         <v>137</v>
@@ -4241,10 +4181,10 @@
         <v>19330051920440</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D26" t="s">
         <v>138</v>
@@ -4258,10 +4198,10 @@
         <v>19330051920345</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D27" t="s">
         <v>139</v>
@@ -4275,10 +4215,10 @@
         <v>19330051920346</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
         <v>140</v>
@@ -4292,10 +4232,10 @@
         <v>19330051920350</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
         <v>141</v>
@@ -4309,10 +4249,10 @@
         <v>19330051920351</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D30" t="s">
         <v>142</v>
@@ -4326,10 +4266,10 @@
         <v>19330051920352</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D31" t="s">
         <v>143</v>
@@ -4343,10 +4283,10 @@
         <v>19330051920354</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D32" t="s">
         <v>144</v>
@@ -4360,10 +4300,10 @@
         <v>19330051920353</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D33" t="s">
         <v>145</v>
@@ -4414,13 +4354,13 @@
         <v>19330051920338</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -4437,13 +4377,13 @@
         <v>19330051920338</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4460,10 +4400,10 @@
         <v>19330051920353</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
         <v>145</v>
@@ -4483,10 +4423,10 @@
         <v>19330051920353</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D5" t="s">
         <v>145</v>
@@ -4506,13 +4446,13 @@
         <v>19330051920307</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -4529,13 +4469,13 @@
         <v>19330051920312</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4552,13 +4492,13 @@
         <v>19330051920316</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -4575,13 +4515,13 @@
         <v>19330051920323</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -4598,13 +4538,13 @@
         <v>19330051920325</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -4621,13 +4561,13 @@
         <v>19330051920330</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4644,13 +4584,13 @@
         <v>19330051920337</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -4667,10 +4607,10 @@
         <v>19330051920352</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D13" t="s">
         <v>143</v>

--- a/grupos/6APV - Estadisticos 20212.xlsx
+++ b/grupos/6APV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -179,15 +179,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
     <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
@@ -206,256 +206,256 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>ARRIETA</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MANUEL</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>PATIÑO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>SANDOVAL</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>XOLIO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>NAVA</t>
+  </si>
+  <si>
+    <t>ARENAS</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>AULIS</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
     <t>CAMPOS</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>CARLO HUMBERTO</t>
+  </si>
+  <si>
+    <t>JESUS ALBERTO</t>
+  </si>
+  <si>
+    <t>JOSMAR ANTONIO</t>
+  </si>
+  <si>
+    <t>KEVIN HONAM</t>
+  </si>
+  <si>
+    <t>GIOVANNI</t>
+  </si>
+  <si>
+    <t>SAUL ESTEBAN</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>ABRAHAM</t>
+  </si>
+  <si>
+    <t>ARELY</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>JESUS MANUEL</t>
+  </si>
+  <si>
+    <t>RUBEN</t>
+  </si>
+  <si>
+    <t>LUZ ABRIL</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>VICTOR YAHIR</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>ANDREA YAMILET</t>
+  </si>
+  <si>
+    <t>CRISTOPHER ENRIQUE</t>
+  </si>
+  <si>
+    <t>CARLOS FERNANDO</t>
+  </si>
+  <si>
     <t>JESUS ARMANDO</t>
   </si>
   <si>
+    <t>CIELO IVETTE</t>
+  </si>
+  <si>
+    <t>GWINETH</t>
+  </si>
+  <si>
+    <t>YOSEF OMAR</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>HERSON ELIAS</t>
+  </si>
+  <si>
     <t>JOEL</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>ARRIETA</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MANUEL</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>PATIÑO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>XOLIO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>NAVA</t>
-  </si>
-  <si>
-    <t>ARENAS</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>AULIS</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>CARLO HUMBERTO</t>
-  </si>
-  <si>
-    <t>JESUS ALBERTO</t>
-  </si>
-  <si>
-    <t>JOSMAR ANTONIO</t>
-  </si>
-  <si>
-    <t>KEVIN HONAM</t>
-  </si>
-  <si>
-    <t>GIOVANNI</t>
-  </si>
-  <si>
-    <t>SAUL ESTEBAN</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ABRAHAM</t>
-  </si>
-  <si>
-    <t>ARELY</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>RUBEN</t>
-  </si>
-  <si>
-    <t>LUZ ABRIL</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>VICTOR YAHIR</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>ANDREA YAMILET</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ENRIQUE</t>
-  </si>
-  <si>
-    <t>CARLOS FERNANDO</t>
-  </si>
-  <si>
-    <t>CIELO IVETTE</t>
-  </si>
-  <si>
-    <t>GWINETH</t>
-  </si>
-  <si>
-    <t>YOSEF OMAR</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>ADAN</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>HERSON ELIAS</t>
   </si>
 </sst>
 </file>
@@ -983,16 +983,16 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
         <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
         <v>9</v>
@@ -1001,7 +1001,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -1010,7 +1010,7 @@
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1042,10 +1042,10 @@
         <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>6</v>
@@ -1060,16 +1060,16 @@
         <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
         <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>6</v>
@@ -1078,10 +1078,10 @@
         <v>6</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -1137,16 +1137,16 @@
         <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
         <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
         <v>9</v>
@@ -1155,16 +1155,16 @@
         <v>9</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1214,16 +1214,16 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
         <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>8</v>
@@ -1232,16 +1232,16 @@
         <v>9</v>
       </c>
       <c r="V7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1291,16 +1291,16 @@
         <v>7</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R8">
         <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1309,7 +1309,7 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>6</v>
@@ -1318,7 +1318,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1368,16 +1368,16 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
         <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1386,16 +1386,16 @@
         <v>10</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1445,16 +1445,16 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
         <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1466,7 +1466,7 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1522,16 +1522,16 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
         <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1540,10 +1540,10 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>8</v>
@@ -1599,16 +1599,16 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
         <v>5</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
         <v>7</v>
@@ -1617,10 +1617,10 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -1676,16 +1676,16 @@
         <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
         <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>7</v>
@@ -1694,7 +1694,7 @@
         <v>9</v>
       </c>
       <c r="V13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1703,7 +1703,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1753,16 +1753,16 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
         <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1830,16 +1830,16 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
         <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1857,7 +1857,7 @@
         <v>9</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1907,16 +1907,16 @@
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>7</v>
@@ -1928,7 +1928,7 @@
         <v>7</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -1984,16 +1984,16 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
         <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -2002,7 +2002,7 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -2061,16 +2061,16 @@
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
         <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T18">
         <v>7</v>
@@ -2082,7 +2082,7 @@
         <v>7</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>8</v>
@@ -2138,16 +2138,16 @@
         <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
         <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -2156,10 +2156,10 @@
         <v>10</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>10</v>
@@ -2206,7 +2206,7 @@
         <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>7</v>
@@ -2215,16 +2215,16 @@
         <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
         <v>7</v>
@@ -2233,10 +2233,10 @@
         <v>6</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>5</v>
@@ -2292,16 +2292,16 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
         <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -2310,16 +2310,16 @@
         <v>10</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2369,16 +2369,16 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
         <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2387,7 +2387,7 @@
         <v>7</v>
       </c>
       <c r="V22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -2396,7 +2396,7 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2446,16 +2446,16 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>10</v>
@@ -2523,16 +2523,16 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
         <v>5</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>6</v>
@@ -2550,7 +2550,7 @@
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2600,16 +2600,16 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
         <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2621,7 +2621,7 @@
         <v>8</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>8</v>
@@ -2677,16 +2677,16 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
         <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2698,7 +2698,7 @@
         <v>7</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -2754,16 +2754,16 @@
         <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R27">
         <v>7</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
         <v>9</v>
@@ -2772,10 +2772,10 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -2831,16 +2831,16 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2872,10 +2872,10 @@
         <v>5</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F29">
         <v>5</v>
@@ -2890,10 +2890,10 @@
         <v>5</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
         <v>5</v>
@@ -2908,16 +2908,16 @@
         <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R29">
         <v>5</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T29">
         <v>5</v>
@@ -2926,10 +2926,10 @@
         <v>5</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X29">
         <v>5</v>
@@ -2967,10 +2967,10 @@
         <v>9</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>5</v>
@@ -2985,16 +2985,16 @@
         <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
         <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T30">
         <v>7</v>
@@ -3003,10 +3003,10 @@
         <v>8</v>
       </c>
       <c r="V30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>5</v>
@@ -3062,16 +3062,16 @@
         <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R31">
         <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -3083,7 +3083,7 @@
         <v>7</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>8</v>
@@ -3139,16 +3139,16 @@
         <v>6</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
         <v>7</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
         <v>8</v>
@@ -3198,16 +3198,16 @@
         <v>6</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L33">
         <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N33">
         <v>6</v>
@@ -3216,16 +3216,16 @@
         <v>6</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R33">
         <v>7</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
         <v>7</v>
@@ -3234,10 +3234,10 @@
         <v>7</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X33">
         <v>5</v>
@@ -3293,16 +3293,16 @@
         <v>6</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R34">
         <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
         <v>7</v>
@@ -3311,16 +3311,16 @@
         <v>6</v>
       </c>
       <c r="V34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>6</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3334,7 +3334,7 @@
         <v>5</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E35">
         <v>5</v>
@@ -3352,10 +3352,10 @@
         <v>5</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L35">
         <v>5</v>
@@ -3370,16 +3370,16 @@
         <v>5</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R35">
         <v>5</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T35">
         <v>5</v>
@@ -3388,7 +3388,7 @@
         <v>5</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W35">
         <v>5</v>
@@ -3453,7 +3453,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -3462,19 +3462,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>59.38</v>
+        <v>75</v>
       </c>
       <c r="G2">
-        <v>40.63</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3494,83 +3494,83 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>62.5</v>
+        <v>87.5</v>
       </c>
       <c r="G3">
-        <v>31.25</v>
+        <v>12.5</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4">
         <v>32</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>65.63</v>
+        <v>87.5</v>
       </c>
       <c r="G4">
-        <v>31.25</v>
+        <v>12.5</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C5">
         <v>32</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>75</v>
+        <v>90.63</v>
       </c>
       <c r="G5">
-        <v>25</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3650,7 +3650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3675,66 +3675,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920347</v>
-      </c>
-      <c r="B2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920347</v>
-      </c>
-      <c r="B3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920355</v>
-      </c>
-      <c r="B4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -3770,47 +3710,47 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920347</v>
+        <v>19330051920307</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920355</v>
+        <v>19330051920308</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920307</v>
+        <v>19330051920309</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
         <v>116</v>
@@ -3821,13 +3761,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920308</v>
+        <v>19330051920311</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
         <v>117</v>
@@ -3838,13 +3778,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920309</v>
+        <v>19330051920312</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
         <v>118</v>
@@ -3855,13 +3795,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920311</v>
+        <v>19330051920316</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
         <v>119</v>
@@ -3872,13 +3812,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920312</v>
+        <v>19330051920318</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
         <v>120</v>
@@ -3889,13 +3829,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920316</v>
+        <v>19330051920319</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
         <v>121</v>
@@ -3906,13 +3846,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920318</v>
+        <v>19330051920323</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
         <v>122</v>
@@ -3923,13 +3863,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920319</v>
+        <v>19330051920441</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
         <v>123</v>
@@ -3940,13 +3880,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920323</v>
+        <v>19330051920325</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
         <v>124</v>
@@ -3957,13 +3897,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920441</v>
+        <v>19330051920321</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
         <v>125</v>
@@ -3974,13 +3914,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920325</v>
+        <v>19330051920330</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
         <v>126</v>
@@ -3991,13 +3931,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920321</v>
+        <v>19330051920332</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
         <v>127</v>
@@ -4008,13 +3948,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920330</v>
+        <v>19330051920331</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
         <v>128</v>
@@ -4025,13 +3965,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920332</v>
+        <v>19330051920333</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
         <v>129</v>
@@ -4042,13 +3982,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920331</v>
+        <v>19330051920334</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s">
         <v>130</v>
@@ -4059,13 +3999,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920333</v>
+        <v>19330051920337</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
         <v>131</v>
@@ -4076,13 +4016,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920334</v>
+        <v>19330051920338</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
         <v>132</v>
@@ -4093,13 +4033,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920337</v>
+        <v>19330051920342</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
         <v>133</v>
@@ -4110,13 +4050,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920338</v>
+        <v>19330051920341</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="D22" t="s">
         <v>134</v>
@@ -4127,13 +4067,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920342</v>
+        <v>19330051920344</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
         <v>135</v>
@@ -4144,13 +4084,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920341</v>
+        <v>19330051920347</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
         <v>136</v>
@@ -4161,13 +4101,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920344</v>
+        <v>19330051920440</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
         <v>137</v>
@@ -4178,13 +4118,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920440</v>
+        <v>19330051920345</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s">
         <v>138</v>
@@ -4195,13 +4135,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920345</v>
+        <v>19330051920346</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s">
         <v>139</v>
@@ -4212,13 +4152,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920346</v>
+        <v>19330051920350</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
         <v>140</v>
@@ -4229,13 +4169,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920350</v>
+        <v>19330051920351</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D29" t="s">
         <v>141</v>
@@ -4246,13 +4186,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920351</v>
+        <v>19330051920352</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s">
         <v>142</v>
@@ -4263,13 +4203,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920352</v>
+        <v>19330051920354</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s">
         <v>143</v>
@@ -4280,13 +4220,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920354</v>
+        <v>19330051920353</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D32" t="s">
         <v>144</v>
@@ -4297,13 +4237,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920353</v>
+        <v>19330051920355</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="D33" t="s">
         <v>145</v>
@@ -4319,7 +4259,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4351,22 +4291,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920338</v>
+        <v>19330051920308</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4374,22 +4314,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920338</v>
+        <v>19330051920308</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4397,22 +4337,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920353</v>
+        <v>19330051920350</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4420,19 +4360,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920353</v>
+        <v>19330051920350</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>55</v>
@@ -4443,19 +4383,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920307</v>
+        <v>19330051920321</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
         <v>53</v>
@@ -4466,19 +4406,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920312</v>
+        <v>19330051920334</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
         <v>53</v>
@@ -4489,22 +4429,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920316</v>
+        <v>19330051920352</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4512,116 +4452,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920323</v>
+        <v>19330051920353</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="D9" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920325</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D10" t="s">
-        <v>126</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920330</v>
-      </c>
-      <c r="B11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" t="s">
-        <v>128</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920337</v>
-      </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D12" t="s">
-        <v>133</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19330051920352</v>
-      </c>
-      <c r="B13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C13" t="s">
-        <v>113</v>
-      </c>
-      <c r="D13" t="s">
-        <v>143</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>
